--- a/resources/tool_household_iphra_v2.xlsx
+++ b/resources/tool_household_iphra_v2.xlsx
@@ -5,13 +5,13 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saeed.rahman\Desktop\public_health_resources\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R Projects\SaeedR1987\public_health_resources\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6C717D7-5153-419A-AFD2-A5082DC37215}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FE2C46F-6525-4C7D-94D6-E85269ED0BB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="h2fYSiQvhiNGkrtUsLkSn45g315KWDSA25bD4j3ORM5bRlKWMnBDtzvS6AbBSYAj6ag3ODyY1mEUTQPcGFJ0Tg==" workbookSaltValue="IfpCe47h0g637JARLrp1Sg==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="570" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="survey" sheetId="1" r:id="rId1"/>
@@ -7127,6 +7127,7 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -7145,7 +7146,6 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -7933,7 +7933,7 @@
       </c>
       <c r="P12" s="2"/>
     </row>
-    <row r="13" spans="1:18" s="9" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:18" s="9" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="9">
         <v>10001</v>
       </c>
@@ -7954,7 +7954,7 @@
       </c>
       <c r="P13" s="2"/>
     </row>
-    <row r="14" spans="1:18" s="9" customFormat="1" ht="75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:18" s="9" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A14" s="9">
         <v>10001</v>
       </c>
@@ -9432,7 +9432,7 @@
       <c r="P86" s="7"/>
     </row>
     <row r="87" spans="1:16" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="47">
+      <c r="A87" s="41">
         <v>14301</v>
       </c>
       <c r="B87" s="7" t="s">
@@ -9468,7 +9468,7 @@
       <c r="P87" s="7"/>
     </row>
     <row r="88" spans="1:16" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="47">
+      <c r="A88" s="41">
         <v>14601</v>
       </c>
       <c r="B88" s="7" t="s">
@@ -9506,7 +9506,7 @@
       <c r="P88" s="7"/>
     </row>
     <row r="89" spans="1:16" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="47">
+      <c r="A89" s="41">
         <v>14601</v>
       </c>
       <c r="B89" s="7" t="s">
@@ -9537,7 +9537,7 @@
       <c r="P89" s="7"/>
     </row>
     <row r="90" spans="1:16" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="47">
+      <c r="A90" s="41">
         <v>14602</v>
       </c>
       <c r="B90" s="7" t="s">
@@ -9568,7 +9568,7 @@
       <c r="P90" s="7"/>
     </row>
     <row r="91" spans="1:16" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="47">
+      <c r="A91" s="41">
         <v>14602</v>
       </c>
       <c r="B91" s="7" t="s">
@@ -9599,7 +9599,7 @@
       <c r="P91" s="7"/>
     </row>
     <row r="92" spans="1:16" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A92" s="47">
+      <c r="A92" s="41">
         <v>14602</v>
       </c>
       <c r="B92" s="7" t="s">
@@ -9630,7 +9630,7 @@
       <c r="P92" s="7"/>
     </row>
     <row r="93" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="47">
+      <c r="A93" s="41">
         <v>14303</v>
       </c>
       <c r="B93" s="2" t="s">
@@ -9653,7 +9653,7 @@
       </c>
     </row>
     <row r="94" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="47">
+      <c r="A94" s="41">
         <v>14304</v>
       </c>
       <c r="B94" s="2" t="s">
@@ -9676,7 +9676,7 @@
       </c>
     </row>
     <row r="95" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="47">
+      <c r="A95" s="41">
         <v>14305</v>
       </c>
       <c r="B95" s="2" t="s">
@@ -9707,7 +9707,7 @@
       </c>
     </row>
     <row r="97" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A97" s="47">
+      <c r="A97" s="41">
         <v>14401</v>
       </c>
       <c r="B97" s="7" t="s">
@@ -9730,7 +9730,7 @@
       </c>
     </row>
     <row r="98" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="47">
+      <c r="A98" s="41">
         <v>14401</v>
       </c>
       <c r="B98" s="7" t="s">
@@ -9750,7 +9750,7 @@
       </c>
     </row>
     <row r="99" spans="1:11" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="47">
+      <c r="A99" s="41">
         <v>14403</v>
       </c>
       <c r="B99" s="9" t="s">
@@ -9776,7 +9776,7 @@
       </c>
     </row>
     <row r="100" spans="1:11" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A100" s="47">
+      <c r="A100" s="41">
         <v>14403</v>
       </c>
       <c r="B100" s="9" t="s">
@@ -9799,7 +9799,7 @@
       </c>
     </row>
     <row r="101" spans="1:11" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A101" s="47">
+      <c r="A101" s="41">
         <v>14403</v>
       </c>
       <c r="B101" s="9" t="s">
@@ -9836,7 +9836,7 @@
       </c>
     </row>
     <row r="103" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A103" s="47">
+      <c r="A103" s="41">
         <v>11204</v>
       </c>
       <c r="B103" s="2" t="s">
@@ -9862,7 +9862,7 @@
       </c>
     </row>
     <row r="104" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A104" s="47">
+      <c r="A104" s="41">
         <v>11204</v>
       </c>
       <c r="B104" s="2" t="s">
@@ -9888,7 +9888,7 @@
       </c>
     </row>
     <row r="105" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A105" s="47">
+      <c r="A105" s="41">
         <v>11204</v>
       </c>
       <c r="B105" s="2" t="s">
@@ -9914,7 +9914,7 @@
       </c>
     </row>
     <row r="106" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A106" s="47">
+      <c r="A106" s="41">
         <v>11204</v>
       </c>
       <c r="B106" s="2" t="s">
@@ -9934,7 +9934,7 @@
       </c>
     </row>
     <row r="107" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="47">
+      <c r="A107" s="41">
         <v>11204</v>
       </c>
       <c r="B107" s="2" t="s">
@@ -9954,7 +9954,7 @@
       </c>
     </row>
     <row r="108" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A108" s="47">
+      <c r="A108" s="41">
         <v>11204</v>
       </c>
       <c r="B108" s="2" t="s">
@@ -9980,7 +9980,7 @@
       </c>
     </row>
     <row r="109" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A109" s="47">
+      <c r="A109" s="41">
         <v>11204</v>
       </c>
       <c r="B109" s="2" t="s">
@@ -10000,7 +10000,7 @@
       </c>
     </row>
     <row r="110" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A110" s="47">
+      <c r="A110" s="41">
         <v>11204</v>
       </c>
       <c r="B110" s="2" t="s">
@@ -10026,7 +10026,7 @@
       </c>
     </row>
     <row r="111" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A111" s="47">
+      <c r="A111" s="41">
         <v>11204</v>
       </c>
       <c r="B111" s="2" t="s">
@@ -10046,7 +10046,7 @@
       </c>
     </row>
     <row r="112" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A112" s="47">
+      <c r="A112" s="41">
         <v>11204</v>
       </c>
       <c r="B112" s="2" t="s">
@@ -10066,7 +10066,7 @@
       </c>
     </row>
     <row r="113" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A113" s="47">
+      <c r="A113" s="41">
         <v>11204</v>
       </c>
       <c r="B113" s="2" t="s">
@@ -10092,7 +10092,7 @@
       </c>
     </row>
     <row r="114" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A114" s="47">
+      <c r="A114" s="41">
         <v>11204</v>
       </c>
       <c r="B114" s="2" t="s">
@@ -10118,7 +10118,7 @@
       </c>
     </row>
     <row r="115" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A115" s="47">
+      <c r="A115" s="41">
         <v>11205</v>
       </c>
       <c r="B115" s="2" t="s">
@@ -10153,7 +10153,7 @@
       </c>
     </row>
     <row r="116" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A116" s="47">
+      <c r="A116" s="41">
         <v>11205</v>
       </c>
       <c r="B116" s="2" t="s">
@@ -10188,7 +10188,7 @@
       </c>
     </row>
     <row r="117" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A117" s="47">
+      <c r="A117" s="41">
         <v>11205</v>
       </c>
       <c r="B117" s="2" t="s">
@@ -10223,7 +10223,7 @@
       </c>
     </row>
     <row r="118" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A118" s="47">
+      <c r="A118" s="41">
         <v>11205</v>
       </c>
       <c r="B118" s="2" t="s">
@@ -10258,7 +10258,7 @@
       </c>
     </row>
     <row r="119" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A119" s="47">
+      <c r="A119" s="41">
         <v>11205</v>
       </c>
       <c r="B119" s="2" t="s">
@@ -10287,7 +10287,7 @@
       </c>
     </row>
     <row r="120" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A120" s="47">
+      <c r="A120" s="41">
         <v>11205</v>
       </c>
       <c r="B120" s="2" t="s">
@@ -10316,7 +10316,7 @@
       </c>
     </row>
     <row r="121" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A121" s="47">
+      <c r="A121" s="41">
         <v>11205</v>
       </c>
       <c r="B121" s="2" t="s">
@@ -10345,7 +10345,7 @@
       </c>
     </row>
     <row r="122" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A122" s="47">
+      <c r="A122" s="41">
         <v>11205</v>
       </c>
       <c r="B122" s="2" t="s">
@@ -10380,7 +10380,7 @@
       </c>
     </row>
     <row r="123" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A123" s="47">
+      <c r="A123" s="41">
         <v>11205</v>
       </c>
       <c r="B123" s="2" t="s">
@@ -10415,7 +10415,7 @@
       </c>
     </row>
     <row r="124" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A124" s="47">
+      <c r="A124" s="41">
         <v>11201</v>
       </c>
       <c r="B124" t="s">
@@ -10435,7 +10435,7 @@
       </c>
     </row>
     <row r="125" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A125" s="47">
+      <c r="A125" s="41">
         <v>11201</v>
       </c>
       <c r="B125" t="s">
@@ -10458,7 +10458,7 @@
       </c>
     </row>
     <row r="126" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A126" s="47">
+      <c r="A126" s="41">
         <v>11201</v>
       </c>
       <c r="B126" t="s">
@@ -10478,7 +10478,7 @@
       </c>
     </row>
     <row r="127" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A127" s="47">
+      <c r="A127" s="41">
         <v>11201</v>
       </c>
       <c r="B127" t="s">
@@ -10501,7 +10501,7 @@
       </c>
     </row>
     <row r="128" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A128" s="47">
+      <c r="A128" s="41">
         <v>11201</v>
       </c>
       <c r="B128" t="s">
@@ -10521,7 +10521,7 @@
       </c>
     </row>
     <row r="129" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A129" s="47">
+      <c r="A129" s="41">
         <v>11201</v>
       </c>
       <c r="B129" t="s">
@@ -10544,7 +10544,7 @@
       </c>
     </row>
     <row r="130" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A130" s="47">
+      <c r="A130" s="41">
         <v>11202</v>
       </c>
       <c r="B130" s="2" t="s">
@@ -10573,7 +10573,7 @@
       </c>
     </row>
     <row r="131" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A131" s="47">
+      <c r="A131" s="41">
         <v>11202</v>
       </c>
       <c r="B131" s="2" t="s">
@@ -10602,7 +10602,7 @@
       </c>
     </row>
     <row r="132" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A132" s="47">
+      <c r="A132" s="41">
         <v>11202</v>
       </c>
       <c r="B132" s="2" t="s">
@@ -10631,7 +10631,7 @@
       </c>
     </row>
     <row r="133" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A133" s="47">
+      <c r="A133" s="41">
         <v>11202</v>
       </c>
       <c r="B133" s="2" t="s">
@@ -10666,7 +10666,7 @@
       </c>
     </row>
     <row r="134" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A134" s="47">
+      <c r="A134" s="41">
         <v>11202</v>
       </c>
       <c r="B134" s="2" t="s">
@@ -10695,7 +10695,7 @@
       </c>
     </row>
     <row r="135" spans="1:15" s="22" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A135" s="47">
+      <c r="A135" s="41">
         <v>11203</v>
       </c>
       <c r="B135" s="2" t="s">
@@ -10718,7 +10718,7 @@
       </c>
     </row>
     <row r="136" spans="1:15" s="22" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A136" s="47">
+      <c r="A136" s="41">
         <v>11203</v>
       </c>
       <c r="B136" s="2" t="s">
@@ -10741,7 +10741,7 @@
       </c>
     </row>
     <row r="137" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A137" s="47">
+      <c r="A137" s="41">
         <v>11301</v>
       </c>
       <c r="B137" t="s">
@@ -10764,7 +10764,7 @@
       </c>
     </row>
     <row r="138" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A138" s="47">
+      <c r="A138" s="41">
         <v>11301</v>
       </c>
       <c r="B138" t="s">
@@ -10787,7 +10787,7 @@
       </c>
     </row>
     <row r="139" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A139" s="47">
+      <c r="A139" s="41">
         <v>11301</v>
       </c>
       <c r="B139" t="s">
@@ -10813,7 +10813,7 @@
       </c>
     </row>
     <row r="140" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A140" s="47">
+      <c r="A140" s="41">
         <v>11301</v>
       </c>
       <c r="B140" t="s">
@@ -10836,7 +10836,7 @@
       </c>
     </row>
     <row r="141" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A141" s="47">
+      <c r="A141" s="41">
         <v>11301</v>
       </c>
       <c r="B141" t="s">
@@ -10862,7 +10862,7 @@
       </c>
     </row>
     <row r="142" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A142" s="47">
+      <c r="A142" s="41">
         <v>11301</v>
       </c>
       <c r="B142" t="s">
@@ -10885,7 +10885,7 @@
       </c>
     </row>
     <row r="143" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A143" s="47">
+      <c r="A143" s="41">
         <v>11401</v>
       </c>
       <c r="B143" t="s">
@@ -10914,7 +10914,7 @@
       </c>
     </row>
     <row r="144" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A144" s="47">
+      <c r="A144" s="41">
         <v>11401</v>
       </c>
       <c r="B144" t="s">
@@ -10937,7 +10937,7 @@
       </c>
     </row>
     <row r="145" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A145" s="47">
+      <c r="A145" s="41">
         <v>11501</v>
       </c>
       <c r="B145" t="s">
@@ -10957,7 +10957,7 @@
       </c>
     </row>
     <row r="146" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A146" s="47">
+      <c r="A146" s="41">
         <v>11501</v>
       </c>
       <c r="B146" t="s">
@@ -10980,7 +10980,7 @@
       </c>
     </row>
     <row r="147" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A147" s="47">
+      <c r="A147" s="41">
         <v>11502</v>
       </c>
       <c r="B147" t="s">
@@ -11000,7 +11000,7 @@
       </c>
     </row>
     <row r="148" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A148" s="47">
+      <c r="A148" s="41">
         <v>11502</v>
       </c>
       <c r="B148" t="s">
@@ -11023,7 +11023,7 @@
       </c>
     </row>
     <row r="149" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A149" s="47">
+      <c r="A149" s="41">
         <v>12201</v>
       </c>
       <c r="B149" s="2" t="s">
@@ -11046,7 +11046,7 @@
       </c>
     </row>
     <row r="150" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A150" s="47">
+      <c r="A150" s="41">
         <v>12201</v>
       </c>
       <c r="B150" s="2" t="s">
@@ -11069,7 +11069,7 @@
       </c>
     </row>
     <row r="151" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A151" s="47">
+      <c r="A151" s="41">
         <v>12201</v>
       </c>
       <c r="B151" s="2" t="s">
@@ -11092,7 +11092,7 @@
       </c>
     </row>
     <row r="152" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A152" s="47">
+      <c r="A152" s="41">
         <v>12201</v>
       </c>
       <c r="B152" s="2" t="s">
@@ -11115,7 +11115,7 @@
       </c>
     </row>
     <row r="153" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A153" s="47">
+      <c r="A153" s="41">
         <v>12201</v>
       </c>
       <c r="B153" s="2" t="s">
@@ -11138,7 +11138,7 @@
       </c>
     </row>
     <row r="154" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A154" s="47">
+      <c r="A154" s="41">
         <v>12201</v>
       </c>
       <c r="B154" s="2" t="s">
@@ -11161,7 +11161,7 @@
       </c>
     </row>
     <row r="155" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A155" s="47">
+      <c r="A155" s="41">
         <v>12301</v>
       </c>
       <c r="B155" s="2" t="s">
@@ -11181,7 +11181,7 @@
       </c>
     </row>
     <row r="156" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A156" s="47">
+      <c r="A156" s="41">
         <v>12301</v>
       </c>
       <c r="B156" s="2" t="s">
@@ -11201,7 +11201,7 @@
       </c>
     </row>
     <row r="157" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A157" s="47">
+      <c r="A157" s="41">
         <v>12301</v>
       </c>
       <c r="B157" s="2" t="s">
@@ -11221,7 +11221,7 @@
       </c>
     </row>
     <row r="158" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A158" s="47">
+      <c r="A158" s="41">
         <v>12301</v>
       </c>
       <c r="B158" s="2" t="s">
@@ -11241,7 +11241,7 @@
       </c>
     </row>
     <row r="159" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A159" s="47">
+      <c r="A159" s="41">
         <v>12301</v>
       </c>
       <c r="B159" s="2" t="s">
@@ -11261,7 +11261,7 @@
       </c>
     </row>
     <row r="160" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A160" s="47">
+      <c r="A160" s="41">
         <v>12301</v>
       </c>
       <c r="B160" s="2" t="s">
@@ -11281,7 +11281,7 @@
       </c>
     </row>
     <row r="161" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A161" s="47">
+      <c r="A161" s="41">
         <v>12301</v>
       </c>
       <c r="B161" s="2" t="s">
@@ -11301,7 +11301,7 @@
       </c>
     </row>
     <row r="162" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A162" s="47">
+      <c r="A162" s="41">
         <v>12301</v>
       </c>
       <c r="B162" s="2" t="s">
@@ -11321,7 +11321,7 @@
       </c>
     </row>
     <row r="163" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A163" s="47">
+      <c r="A163" s="41">
         <v>12301</v>
       </c>
       <c r="B163" s="2" t="s">
@@ -11341,7 +11341,7 @@
       </c>
     </row>
     <row r="164" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A164" s="47">
+      <c r="A164" s="41">
         <v>12301</v>
       </c>
       <c r="B164" s="2" t="s">
@@ -11361,7 +11361,7 @@
       </c>
     </row>
     <row r="165" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A165" s="47">
+      <c r="A165" s="41">
         <v>12302</v>
       </c>
       <c r="B165" s="2" t="s">
@@ -11381,7 +11381,7 @@
       </c>
     </row>
     <row r="166" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A166" s="47">
+      <c r="A166" s="41">
         <v>12303</v>
       </c>
       <c r="B166" s="2" t="s">
@@ -11396,7 +11396,7 @@
       <c r="I166" s="9"/>
     </row>
     <row r="167" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A167" s="47">
+      <c r="A167" s="41">
         <v>12303</v>
       </c>
       <c r="B167" s="2" t="s">
@@ -11428,7 +11428,7 @@
       </c>
     </row>
     <row r="168" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A168" s="47">
+      <c r="A168" s="41">
         <v>12303</v>
       </c>
       <c r="B168" s="2" t="s">
@@ -11451,7 +11451,7 @@
       </c>
     </row>
     <row r="169" spans="1:11" s="21" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A169" s="47" t="s">
+      <c r="A169" s="41" t="s">
         <v>2161</v>
       </c>
       <c r="B169" s="3" t="s">
@@ -11465,7 +11465,7 @@
       </c>
     </row>
     <row r="170" spans="1:11" s="21" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A170" s="47">
+      <c r="A170" s="41">
         <v>13101</v>
       </c>
       <c r="B170" s="39" t="s">
@@ -11482,7 +11482,7 @@
       </c>
     </row>
     <row r="171" spans="1:11" s="21" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A171" s="47">
+      <c r="A171" s="41">
         <v>13101</v>
       </c>
       <c r="B171" s="39" t="s">
@@ -11499,7 +11499,7 @@
       </c>
     </row>
     <row r="172" spans="1:11" s="21" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A172" s="47">
+      <c r="A172" s="41">
         <v>13104</v>
       </c>
       <c r="B172" s="39" t="s">
@@ -11516,7 +11516,7 @@
       </c>
     </row>
     <row r="173" spans="1:11" s="21" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A173" s="47">
+      <c r="A173" s="41">
         <v>13104</v>
       </c>
       <c r="B173" s="39" t="s">
@@ -11533,7 +11533,7 @@
       </c>
     </row>
     <row r="174" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A174" s="47" t="s">
+      <c r="A174" s="41" t="s">
         <v>2166</v>
       </c>
       <c r="B174" s="3" t="s">
@@ -11550,7 +11550,7 @@
       </c>
     </row>
     <row r="175" spans="1:11" s="23" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A175" s="47" t="s">
+      <c r="A175" s="41" t="s">
         <v>2152</v>
       </c>
       <c r="B175" s="7" t="s">
@@ -11570,7 +11570,7 @@
       </c>
     </row>
     <row r="176" spans="1:11" s="23" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A176" s="47" t="s">
+      <c r="A176" s="41" t="s">
         <v>2152</v>
       </c>
       <c r="B176" s="7" t="s">
@@ -11593,7 +11593,7 @@
       </c>
     </row>
     <row r="177" spans="1:12" s="23" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A177" s="47">
+      <c r="A177" s="41">
         <v>11802</v>
       </c>
       <c r="B177" s="7" t="s">
@@ -11614,7 +11614,7 @@
       <c r="J177" s="7"/>
     </row>
     <row r="178" spans="1:12" s="23" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A178" s="47">
+      <c r="A178" s="41">
         <v>11802</v>
       </c>
       <c r="B178" s="7" t="s">
@@ -11646,7 +11646,7 @@
       </c>
     </row>
     <row r="179" spans="1:12" s="23" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A179" s="47">
+      <c r="A179" s="41">
         <v>11802</v>
       </c>
       <c r="B179" s="7" t="s">
@@ -11669,7 +11669,7 @@
       </c>
     </row>
     <row r="180" spans="1:12" s="23" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A180" s="47">
+      <c r="A180" s="41">
         <v>12001</v>
       </c>
       <c r="B180" s="7" t="s">
@@ -11696,7 +11696,7 @@
       <c r="J180" s="7"/>
     </row>
     <row r="181" spans="1:12" s="23" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A181" s="47">
+      <c r="A181" s="41">
         <v>12001</v>
       </c>
       <c r="B181" s="7" t="s">
@@ -11720,7 +11720,7 @@
       </c>
     </row>
     <row r="182" spans="1:12" s="23" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A182" s="47">
+      <c r="A182" s="41">
         <v>12002</v>
       </c>
       <c r="B182" s="7" t="s">
@@ -11739,7 +11739,7 @@
       <c r="J182" s="7"/>
     </row>
     <row r="183" spans="1:12" s="23" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A183" s="47">
+      <c r="A183" s="41">
         <v>12002</v>
       </c>
       <c r="B183" s="7" t="s">
@@ -11758,7 +11758,7 @@
       <c r="J183" s="7"/>
     </row>
     <row r="184" spans="1:12" s="23" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A184" s="47">
+      <c r="A184" s="41">
         <v>12002</v>
       </c>
       <c r="B184" s="7" t="s">
@@ -11777,7 +11777,7 @@
       <c r="J184" s="7"/>
     </row>
     <row r="185" spans="1:12" s="23" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A185" s="47">
+      <c r="A185" s="41">
         <v>12002</v>
       </c>
       <c r="B185" s="7" t="s">
@@ -11806,7 +11806,7 @@
       </c>
     </row>
     <row r="186" spans="1:12" s="23" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A186" s="47">
+      <c r="A186" s="41">
         <v>12002</v>
       </c>
       <c r="B186" s="7" t="s">
@@ -11830,7 +11830,7 @@
       </c>
     </row>
     <row r="187" spans="1:12" s="23" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A187" s="47">
+      <c r="A187" s="41">
         <v>12002</v>
       </c>
       <c r="B187" s="7" t="s">
@@ -11859,7 +11859,7 @@
       </c>
     </row>
     <row r="188" spans="1:12" s="23" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A188" s="47">
+      <c r="A188" s="41">
         <v>12002</v>
       </c>
       <c r="B188" s="7" t="s">
@@ -11883,7 +11883,7 @@
       </c>
     </row>
     <row r="189" spans="1:12" s="23" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A189" s="47" t="s">
+      <c r="A189" s="41" t="s">
         <v>2153</v>
       </c>
       <c r="B189" s="7" t="s">
@@ -11907,7 +11907,7 @@
       <c r="L189" s="24"/>
     </row>
     <row r="190" spans="1:12" s="23" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A190" s="47" t="s">
+      <c r="A190" s="41" t="s">
         <v>2153</v>
       </c>
       <c r="B190" s="7" t="s">
@@ -11936,7 +11936,7 @@
       </c>
     </row>
     <row r="191" spans="1:12" s="23" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A191" s="47" t="s">
+      <c r="A191" s="41" t="s">
         <v>2153</v>
       </c>
       <c r="B191" s="7" t="s">
@@ -11960,7 +11960,7 @@
       <c r="L191" s="24"/>
     </row>
     <row r="192" spans="1:12" s="23" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A192" s="47">
+      <c r="A192" s="41">
         <v>12003</v>
       </c>
       <c r="B192" s="7" t="s">
@@ -11981,7 +11981,7 @@
       <c r="J192" s="7"/>
     </row>
     <row r="193" spans="1:13" s="23" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A193" s="47">
+      <c r="A193" s="41">
         <v>12003</v>
       </c>
       <c r="B193" s="7" t="s">
@@ -12004,7 +12004,7 @@
       </c>
     </row>
     <row r="194" spans="1:13" s="22" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A194" s="47">
+      <c r="A194" s="41">
         <v>12101</v>
       </c>
       <c r="B194" s="9" t="s">
@@ -12027,7 +12027,7 @@
       </c>
     </row>
     <row r="195" spans="1:13" s="22" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A195" s="47">
+      <c r="A195" s="41">
         <v>12101</v>
       </c>
       <c r="B195" s="9" t="s">
@@ -12053,7 +12053,7 @@
       </c>
     </row>
     <row r="196" spans="1:13" s="22" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A196" s="47">
+      <c r="A196" s="41">
         <v>10901</v>
       </c>
       <c r="B196" s="9" t="s">
@@ -12072,7 +12072,7 @@
       <c r="J196" s="9"/>
       <c r="K196" s="9"/>
     </row>
-    <row r="197" spans="1:13" s="22" customFormat="1" ht="75" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:13" s="22" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A197" s="29">
         <v>11702</v>
       </c>
@@ -12093,7 +12093,7 @@
       <c r="K197" s="9"/>
     </row>
     <row r="198" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A198" s="47" t="s">
+      <c r="A198" s="41" t="s">
         <v>2154</v>
       </c>
       <c r="B198" t="s">
@@ -12113,7 +12113,7 @@
       </c>
     </row>
     <row r="199" spans="1:13" s="23" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A199" s="47" t="s">
+      <c r="A199" s="41" t="s">
         <v>2154</v>
       </c>
       <c r="B199" s="7" t="s">
@@ -12140,7 +12140,7 @@
       </c>
     </row>
     <row r="200" spans="1:13" s="26" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A200" s="47">
+      <c r="A200" s="41">
         <v>10901</v>
       </c>
       <c r="B200" s="25" t="s">
@@ -12165,7 +12165,7 @@
       </c>
     </row>
     <row r="201" spans="1:13" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A201" s="47">
+      <c r="A201" s="41">
         <v>10901</v>
       </c>
       <c r="B201" s="17" t="s">
@@ -12179,7 +12179,7 @@
       </c>
     </row>
     <row r="202" spans="1:13" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A202" s="47">
+      <c r="A202" s="41">
         <v>10901</v>
       </c>
       <c r="B202" s="17" t="s">
@@ -12193,7 +12193,7 @@
       </c>
     </row>
     <row r="203" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A203" s="47">
+      <c r="A203" s="41">
         <v>10901</v>
       </c>
       <c r="B203" s="9" t="s">
@@ -12213,7 +12213,7 @@
       </c>
     </row>
     <row r="204" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A204" s="47">
+      <c r="A204" s="41">
         <v>10901</v>
       </c>
       <c r="B204" s="9" t="s">
@@ -12236,7 +12236,7 @@
       </c>
     </row>
     <row r="205" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A205" s="47">
+      <c r="A205" s="41">
         <v>10901</v>
       </c>
       <c r="B205" s="9" t="s">
@@ -12262,7 +12262,7 @@
       </c>
     </row>
     <row r="206" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A206" s="47">
+      <c r="A206" s="41">
         <v>10901</v>
       </c>
       <c r="B206" s="9" t="s">
@@ -12285,7 +12285,7 @@
       </c>
     </row>
     <row r="207" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A207" s="47">
+      <c r="A207" s="41">
         <v>10901</v>
       </c>
       <c r="B207" s="9" t="s">
@@ -12308,7 +12308,7 @@
       </c>
     </row>
     <row r="208" spans="1:13" s="26" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A208" s="47">
+      <c r="A208" s="41">
         <v>10901</v>
       </c>
       <c r="B208" s="25" t="s">
@@ -12320,7 +12320,7 @@
       <c r="K208" s="25"/>
     </row>
     <row r="209" spans="1:11" s="23" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A209" s="47">
+      <c r="A209" s="41">
         <v>11101</v>
       </c>
       <c r="B209" s="7" t="s">
@@ -12341,7 +12341,7 @@
       <c r="J209" s="7"/>
     </row>
     <row r="210" spans="1:11" s="22" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A210" s="47">
+      <c r="A210" s="41">
         <v>11701</v>
       </c>
       <c r="B210" s="9" t="s">
@@ -12362,7 +12362,7 @@
       <c r="J210" s="9"/>
     </row>
     <row r="211" spans="1:11" s="22" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A211" s="47">
+      <c r="A211" s="41">
         <v>11701</v>
       </c>
       <c r="B211" s="9" t="s">
@@ -12383,7 +12383,7 @@
       <c r="J211" s="9"/>
     </row>
     <row r="212" spans="1:11" s="22" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A212" s="47">
+      <c r="A212" s="41">
         <v>11701</v>
       </c>
       <c r="B212" s="9" t="s">
@@ -12404,7 +12404,7 @@
       <c r="J212" s="9"/>
     </row>
     <row r="213" spans="1:11" s="22" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A213" s="47">
+      <c r="A213" s="41">
         <v>11701</v>
       </c>
       <c r="B213" s="9" t="s">
@@ -12425,7 +12425,7 @@
       <c r="J213" s="9"/>
     </row>
     <row r="214" spans="1:11" s="22" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A214" s="47">
+      <c r="A214" s="41">
         <v>12601</v>
       </c>
       <c r="B214" s="9" t="s">
@@ -12446,7 +12446,7 @@
       <c r="J214" s="9"/>
     </row>
     <row r="215" spans="1:11" s="22" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A215" s="47">
+      <c r="A215" s="41">
         <v>12601</v>
       </c>
       <c r="B215" s="9" t="s">
@@ -12469,7 +12469,7 @@
       </c>
     </row>
     <row r="216" spans="1:11" s="22" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A216" s="47">
+      <c r="A216" s="41">
         <v>12602</v>
       </c>
       <c r="B216" s="9" t="s">
@@ -12581,7 +12581,7 @@
       <c r="K220" s="9"/>
     </row>
     <row r="221" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A221" s="47" t="s">
+      <c r="A221" s="41" t="s">
         <v>2167</v>
       </c>
       <c r="B221" s="3" t="s">
@@ -12598,7 +12598,7 @@
       </c>
     </row>
     <row r="222" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A222" s="47">
+      <c r="A222" s="41">
         <v>12501</v>
       </c>
       <c r="B222" s="7" t="s">
@@ -12618,7 +12618,7 @@
       </c>
     </row>
     <row r="223" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A223" s="47">
+      <c r="A223" s="41">
         <v>12501</v>
       </c>
       <c r="B223" s="7" t="s">
@@ -12641,7 +12641,7 @@
       </c>
     </row>
     <row r="224" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A224" s="47">
+      <c r="A224" s="41">
         <v>12701</v>
       </c>
       <c r="B224" s="7" t="s">
@@ -12661,7 +12661,7 @@
       </c>
     </row>
     <row r="225" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A225" s="47">
+      <c r="A225" s="41">
         <v>12701</v>
       </c>
       <c r="B225" s="7" t="s">
@@ -12681,7 +12681,7 @@
       </c>
     </row>
     <row r="226" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A226" s="47">
+      <c r="A226" s="41">
         <v>12701</v>
       </c>
       <c r="B226" s="7" t="s">
@@ -12704,7 +12704,7 @@
       </c>
     </row>
     <row r="227" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A227" s="47">
+      <c r="A227" s="41">
         <v>12701</v>
       </c>
       <c r="B227" s="7" t="s">
@@ -12727,7 +12727,7 @@
       </c>
     </row>
     <row r="228" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A228" s="47">
+      <c r="A228" s="41">
         <v>12701</v>
       </c>
       <c r="B228" s="7" t="s">
@@ -12750,7 +12750,7 @@
       </c>
     </row>
     <row r="229" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A229" s="47">
+      <c r="A229" s="41">
         <v>12502</v>
       </c>
       <c r="B229" s="7" t="s">
@@ -12782,7 +12782,7 @@
       </c>
     </row>
     <row r="230" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A230" s="47">
+      <c r="A230" s="41">
         <v>12502</v>
       </c>
       <c r="B230" s="7" t="s">
@@ -12805,7 +12805,7 @@
       </c>
     </row>
     <row r="231" spans="1:11" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A231" s="47">
+      <c r="A231" s="41">
         <v>11503</v>
       </c>
       <c r="B231" s="9" t="s">
@@ -12825,7 +12825,7 @@
       </c>
     </row>
     <row r="232" spans="1:11" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A232" s="47">
+      <c r="A232" s="41">
         <v>11503</v>
       </c>
       <c r="B232" s="9" t="s">
@@ -12857,7 +12857,7 @@
       </c>
     </row>
     <row r="233" spans="1:11" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A233" s="47">
+      <c r="A233" s="41">
         <v>11503</v>
       </c>
       <c r="B233" s="9" t="s">
@@ -12880,7 +12880,7 @@
       </c>
     </row>
     <row r="234" spans="1:11" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A234" s="47">
+      <c r="A234" s="41">
         <v>12702</v>
       </c>
       <c r="B234" s="9" t="s">
@@ -12900,7 +12900,7 @@
       </c>
     </row>
     <row r="235" spans="1:11" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A235" s="47">
+      <c r="A235" s="41">
         <v>12702</v>
       </c>
       <c r="B235" s="9" t="s">
@@ -12932,7 +12932,7 @@
       </c>
     </row>
     <row r="236" spans="1:11" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A236" s="47">
+      <c r="A236" s="41">
         <v>12702</v>
       </c>
       <c r="B236" s="9" t="s">
@@ -12955,7 +12955,7 @@
       </c>
     </row>
     <row r="237" spans="1:11" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A237" s="47">
+      <c r="A237" s="41">
         <v>11504</v>
       </c>
       <c r="B237" s="9" t="s">
@@ -12975,7 +12975,7 @@
       </c>
     </row>
     <row r="238" spans="1:11" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A238" s="47">
+      <c r="A238" s="41">
         <v>11504</v>
       </c>
       <c r="B238" s="9" t="s">
@@ -13007,7 +13007,7 @@
       </c>
     </row>
     <row r="239" spans="1:11" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A239" s="47">
+      <c r="A239" s="41">
         <v>11504</v>
       </c>
       <c r="B239" s="9" t="s">
@@ -13030,7 +13030,7 @@
       </c>
     </row>
     <row r="240" spans="1:11" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A240" s="47">
+      <c r="A240" s="41">
         <v>12503</v>
       </c>
       <c r="B240" s="9" t="s">
@@ -13050,7 +13050,7 @@
       </c>
     </row>
     <row r="241" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A241" s="47">
+      <c r="A241" s="41">
         <v>12503</v>
       </c>
       <c r="B241" s="9" t="s">
@@ -13082,7 +13082,7 @@
       </c>
     </row>
     <row r="242" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A242" s="47">
+      <c r="A242" s="41">
         <v>12503</v>
       </c>
       <c r="B242" s="9" t="s">
@@ -13105,7 +13105,7 @@
       </c>
     </row>
     <row r="243" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A243" s="47">
+      <c r="A243" s="41">
         <v>11102</v>
       </c>
       <c r="B243" s="9" t="s">
@@ -13125,7 +13125,7 @@
       </c>
     </row>
     <row r="244" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A244" s="47">
+      <c r="A244" s="41">
         <v>11102</v>
       </c>
       <c r="B244" s="9" t="s">
@@ -13157,7 +13157,7 @@
       </c>
     </row>
     <row r="245" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A245" s="47">
+      <c r="A245" s="41">
         <v>11102</v>
       </c>
       <c r="B245" s="9" t="s">
@@ -13478,7 +13478,7 @@
         <v>775</v>
       </c>
     </row>
-    <row r="262" spans="1:15" ht="105" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:15" ht="75" x14ac:dyDescent="0.25">
       <c r="A262" s="3">
         <v>10701</v>
       </c>
@@ -13510,7 +13510,7 @@
       </c>
     </row>
     <row r="264" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A264" s="47">
+      <c r="A264" s="41">
         <v>13801</v>
       </c>
       <c r="B264" s="7" t="s">
@@ -13533,7 +13533,7 @@
       </c>
     </row>
     <row r="265" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A265" s="47" t="s">
+      <c r="A265" s="41" t="s">
         <v>2133</v>
       </c>
       <c r="B265" t="s">
@@ -13553,7 +13553,7 @@
       </c>
     </row>
     <row r="266" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A266" s="47" t="s">
+      <c r="A266" s="41" t="s">
         <v>2135</v>
       </c>
       <c r="B266" t="s">
@@ -13579,7 +13579,7 @@
       </c>
     </row>
     <row r="267" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A267" s="47">
+      <c r="A267" s="41">
         <v>11402</v>
       </c>
       <c r="B267" t="s">
@@ -13608,7 +13608,7 @@
       </c>
     </row>
     <row r="268" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A268" s="47">
+      <c r="A268" s="41">
         <v>11402</v>
       </c>
       <c r="B268" t="s">
@@ -13631,7 +13631,7 @@
       </c>
     </row>
     <row r="269" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A269" s="47">
+      <c r="A269" s="41">
         <v>10802</v>
       </c>
       <c r="B269" t="s">
@@ -13652,7 +13652,7 @@
       </c>
     </row>
     <row r="270" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A270" s="47">
+      <c r="A270" s="41">
         <v>10802</v>
       </c>
       <c r="B270" t="s">
@@ -13675,7 +13675,7 @@
       </c>
     </row>
     <row r="271" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A271" s="47" t="s">
+      <c r="A271" s="41" t="s">
         <v>2136</v>
       </c>
       <c r="B271" t="s">
@@ -13701,7 +13701,7 @@
       </c>
     </row>
     <row r="272" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A272" s="47" t="s">
+      <c r="A272" s="41" t="s">
         <v>2136</v>
       </c>
       <c r="B272" t="s">
@@ -14117,7 +14117,7 @@
       </c>
     </row>
     <row r="295" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A295" s="47">
+      <c r="A295" s="41">
         <v>13803</v>
       </c>
       <c r="B295" s="2" t="s">
@@ -14137,7 +14137,7 @@
       </c>
     </row>
     <row r="296" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A296" s="47">
+      <c r="A296" s="41">
         <v>13803</v>
       </c>
       <c r="B296" s="2" t="s">
@@ -14765,7 +14765,7 @@
       </c>
     </row>
     <row r="327" spans="1:16" s="22" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A327" s="47" t="s">
+      <c r="A327" s="41" t="s">
         <v>2159</v>
       </c>
       <c r="B327" s="9" t="s">
@@ -14786,7 +14786,7 @@
       <c r="J327" s="9"/>
     </row>
     <row r="328" spans="1:16" s="22" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A328" s="47">
+      <c r="A328" s="41">
         <v>14302</v>
       </c>
       <c r="B328" s="9" t="s">
@@ -14809,7 +14809,7 @@
       </c>
     </row>
     <row r="329" spans="1:16" s="22" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A329" s="47">
+      <c r="A329" s="41">
         <v>14302</v>
       </c>
       <c r="B329" s="9" t="s">
@@ -14832,7 +14832,7 @@
       </c>
     </row>
     <row r="330" spans="1:16" s="22" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A330" s="47" t="s">
+      <c r="A330" s="41" t="s">
         <v>2159</v>
       </c>
       <c r="B330" s="9" t="s">
@@ -14855,7 +14855,7 @@
       </c>
     </row>
     <row r="331" spans="1:16" s="22" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A331" s="47" t="s">
+      <c r="A331" s="41" t="s">
         <v>2159</v>
       </c>
       <c r="B331" s="9" t="s">
@@ -14878,7 +14878,7 @@
       </c>
     </row>
     <row r="332" spans="1:16" s="22" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A332" s="47" t="s">
+      <c r="A332" s="41" t="s">
         <v>2159</v>
       </c>
       <c r="B332" s="9" t="s">
@@ -14969,38 +14969,38 @@
   <conditionalFormatting sqref="C12:C15">
     <cfRule type="duplicateValues" dxfId="19" priority="154"/>
   </conditionalFormatting>
+  <conditionalFormatting sqref="C23">
+    <cfRule type="duplicateValues" dxfId="18" priority="16"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="C24:C28">
-    <cfRule type="duplicateValues" dxfId="18" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="15"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C23">
-    <cfRule type="duplicateValues" dxfId="17" priority="16"/>
+  <conditionalFormatting sqref="C36:C41">
+    <cfRule type="duplicateValues" dxfId="16" priority="184"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C204:C205">
-    <cfRule type="duplicateValues" dxfId="16" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C217:C220">
-    <cfRule type="duplicateValues" dxfId="15" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C264">
-    <cfRule type="duplicateValues" dxfId="14" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C268:C270">
-    <cfRule type="duplicateValues" dxfId="13" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C274:C281 C272">
-    <cfRule type="duplicateValues" dxfId="12" priority="66"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="66"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C292 C29:C35 C42:C74">
-    <cfRule type="duplicateValues" dxfId="11" priority="65"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="65"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C296 C75:C76 C198:C199 C203 C83:C93 C97:C168">
-    <cfRule type="duplicateValues" dxfId="10" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="30"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C297:C1048576 C94:C95 C1:C11 C271 C282:C291 C293:C295 C265:C267 C16:C22 C175:C197 C221:C258 C209:C216 C261:C262 C206:C207">
-    <cfRule type="duplicateValues" dxfId="9" priority="28"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C36:C41">
-    <cfRule type="duplicateValues" dxfId="8" priority="184"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="28"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
@@ -15016,6 +15016,9 @@
     <col min="2" max="2" width="28.42578125" customWidth="1"/>
     <col min="3" max="3" width="38.140625" customWidth="1"/>
     <col min="4" max="4" width="50.42578125" customWidth="1"/>
+    <col min="5" max="5" width="27.5703125" customWidth="1"/>
+    <col min="6" max="6" width="17.140625" customWidth="1"/>
+    <col min="7" max="7" width="25.140625" customWidth="1"/>
     <col min="8" max="8" width="23.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -15042,242 +15045,242 @@
         <v>982</v>
       </c>
     </row>
-    <row r="2" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>10000</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>983</v>
-      </c>
-      <c r="C2" s="2">
-        <v>1</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>984</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>985</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B2" t="s">
+        <v>1010</v>
+      </c>
+      <c r="C2" t="s">
+        <v>848</v>
+      </c>
+      <c r="D2" t="s">
+        <v>1011</v>
+      </c>
+      <c r="E2" t="s">
+        <v>1012</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>10000</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>983</v>
-      </c>
-      <c r="C3" s="2">
-        <v>2</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>986</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>987</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B3" t="s">
+        <v>1010</v>
+      </c>
+      <c r="C3" t="s">
+        <v>1013</v>
+      </c>
+      <c r="D3" t="s">
+        <v>1014</v>
+      </c>
+      <c r="E3" t="s">
+        <v>1015</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>10000</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>983</v>
-      </c>
-      <c r="C4" s="2">
-        <v>3</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>988</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>989</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
+        <v>1016</v>
+      </c>
+      <c r="C4" t="s">
+        <v>848</v>
+      </c>
+      <c r="D4" t="s">
+        <v>1011</v>
+      </c>
+      <c r="E4" t="s">
+        <v>1012</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>10000</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>983</v>
-      </c>
-      <c r="C5" s="2">
-        <v>4</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>990</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>991</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
+        <v>1016</v>
+      </c>
+      <c r="C5" t="s">
+        <v>1013</v>
+      </c>
+      <c r="D5" t="s">
+        <v>1014</v>
+      </c>
+      <c r="E5" t="s">
+        <v>1015</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>10000</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>983</v>
-      </c>
-      <c r="C6" s="2">
-        <v>5</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>992</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>993</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
+        <v>1016</v>
+      </c>
+      <c r="C6" t="s">
+        <v>1017</v>
+      </c>
+      <c r="D6" t="s">
+        <v>1018</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>1019</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>10000</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>994</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>995</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>996</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
+        <v>2089</v>
+      </c>
+      <c r="C7" t="s">
+        <v>848</v>
+      </c>
+      <c r="D7" t="s">
+        <v>1011</v>
+      </c>
+      <c r="E7" t="s">
+        <v>1012</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>10000</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>997</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>995</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>996</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B8" t="s">
+        <v>2089</v>
+      </c>
+      <c r="C8" t="s">
+        <v>1013</v>
+      </c>
+      <c r="D8" t="s">
+        <v>1014</v>
+      </c>
+      <c r="E8" t="s">
+        <v>1015</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>10000</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>998</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>995</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>996</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B9" t="s">
+        <v>2089</v>
+      </c>
+      <c r="C9" t="s">
+        <v>1017</v>
+      </c>
+      <c r="D9" t="s">
+        <v>1018</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>1019</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>10000</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>999</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>995</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>996</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B10" t="s">
+        <v>2089</v>
+      </c>
+      <c r="C10" t="s">
+        <v>1043</v>
+      </c>
+      <c r="D10" t="s">
+        <v>1044</v>
+      </c>
+      <c r="E10" t="s">
+        <v>1045</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>10000</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>1000</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>995</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>996</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B11" t="s">
+        <v>2102</v>
+      </c>
+      <c r="C11" t="s">
+        <v>848</v>
+      </c>
+      <c r="D11" t="s">
+        <v>1011</v>
+      </c>
+      <c r="E11" t="s">
+        <v>1012</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>10000</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>1001</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>995</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>996</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B12" t="s">
+        <v>2102</v>
+      </c>
+      <c r="C12" t="s">
+        <v>1013</v>
+      </c>
+      <c r="D12" t="s">
+        <v>1014</v>
+      </c>
+      <c r="E12" t="s">
+        <v>1015</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>10000</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>1002</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>995</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>996</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B13" t="s">
+        <v>2102</v>
+      </c>
+      <c r="C13" s="40" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D13" s="40" t="s">
+        <v>1857</v>
+      </c>
+      <c r="E13" t="s">
+        <v>1858</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>10000</v>
       </c>
-      <c r="B14" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>1003</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>995</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>996</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B14" t="s">
+        <v>1020</v>
+      </c>
+      <c r="C14" t="s">
+        <v>1021</v>
+      </c>
+      <c r="D14" t="s">
+        <v>1022</v>
+      </c>
+      <c r="E14" t="s">
+        <v>1023</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>10000</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>1004</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>995</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>996</v>
+      <c r="B15" t="s">
+        <v>1020</v>
+      </c>
+      <c r="C15" t="s">
+        <v>1024</v>
+      </c>
+      <c r="D15" t="s">
+        <v>1025</v>
+      </c>
+      <c r="E15" t="s">
+        <v>1026</v>
       </c>
     </row>
     <row r="16" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -15285,16 +15288,16 @@
         <v>10000</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>1005</v>
+        <v>983</v>
+      </c>
+      <c r="C16" s="2">
+        <v>1</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>995</v>
+        <v>984</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>996</v>
+        <v>985</v>
       </c>
     </row>
     <row r="17" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -15302,16 +15305,16 @@
         <v>10000</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>1006</v>
+        <v>983</v>
+      </c>
+      <c r="C17" s="2">
+        <v>2</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>995</v>
+        <v>986</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>996</v>
+        <v>987</v>
       </c>
     </row>
     <row r="18" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -15319,16 +15322,16 @@
         <v>10000</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>1007</v>
+        <v>983</v>
+      </c>
+      <c r="C18" s="2">
+        <v>3</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>995</v>
+        <v>988</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>996</v>
+        <v>989</v>
       </c>
     </row>
     <row r="19" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -15336,16 +15339,16 @@
         <v>10000</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>1008</v>
+        <v>983</v>
+      </c>
+      <c r="C19" s="2">
+        <v>4</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>995</v>
+        <v>990</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>996</v>
+        <v>991</v>
       </c>
     </row>
     <row r="20" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -15353,254 +15356,254 @@
         <v>10000</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>1009</v>
+        <v>983</v>
+      </c>
+      <c r="C20" s="2">
+        <v>5</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>995</v>
+        <v>992</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>996</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+        <v>993</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>10000</v>
       </c>
-      <c r="B21" t="s">
-        <v>1010</v>
-      </c>
-      <c r="C21" t="s">
-        <v>848</v>
-      </c>
-      <c r="D21" t="s">
-        <v>1011</v>
-      </c>
-      <c r="E21" t="s">
-        <v>1012</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B21" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>994</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>995</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>996</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>10000</v>
       </c>
-      <c r="B22" t="s">
-        <v>1010</v>
-      </c>
-      <c r="C22" t="s">
-        <v>1013</v>
-      </c>
-      <c r="D22" t="s">
-        <v>1014</v>
-      </c>
-      <c r="E22" t="s">
-        <v>1015</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B22" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>997</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>995</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>996</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>10000</v>
       </c>
-      <c r="B23" t="s">
-        <v>1016</v>
-      </c>
-      <c r="C23" t="s">
-        <v>848</v>
-      </c>
-      <c r="D23" t="s">
-        <v>1011</v>
-      </c>
-      <c r="E23" t="s">
-        <v>1012</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B23" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>998</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>995</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>996</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>10000</v>
       </c>
-      <c r="B24" t="s">
-        <v>1016</v>
-      </c>
-      <c r="C24" t="s">
-        <v>1013</v>
-      </c>
-      <c r="D24" t="s">
-        <v>1014</v>
-      </c>
-      <c r="E24" t="s">
-        <v>1015</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B24" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>999</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>995</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>996</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>10000</v>
       </c>
-      <c r="B25" t="s">
-        <v>1016</v>
-      </c>
-      <c r="C25" t="s">
-        <v>1017</v>
-      </c>
-      <c r="D25" t="s">
-        <v>1018</v>
-      </c>
-      <c r="E25" s="7" t="s">
-        <v>1019</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B25" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>1000</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>995</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>996</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>10000</v>
       </c>
-      <c r="B26" t="s">
-        <v>2089</v>
-      </c>
-      <c r="C26" t="s">
-        <v>848</v>
-      </c>
-      <c r="D26" t="s">
-        <v>1011</v>
-      </c>
-      <c r="E26" t="s">
-        <v>1012</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B26" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>1001</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>995</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>996</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <v>10000</v>
       </c>
-      <c r="B27" t="s">
-        <v>2089</v>
-      </c>
-      <c r="C27" t="s">
-        <v>1013</v>
-      </c>
-      <c r="D27" t="s">
-        <v>1014</v>
-      </c>
-      <c r="E27" t="s">
-        <v>1015</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B27" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>1002</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>995</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>996</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <v>10000</v>
       </c>
-      <c r="B28" t="s">
-        <v>2089</v>
-      </c>
-      <c r="C28" t="s">
-        <v>1017</v>
-      </c>
-      <c r="D28" t="s">
-        <v>1018</v>
-      </c>
-      <c r="E28" s="7" t="s">
-        <v>1019</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B28" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>1003</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>995</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>996</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <v>10000</v>
       </c>
-      <c r="B29" t="s">
-        <v>2089</v>
-      </c>
-      <c r="C29" t="s">
-        <v>1043</v>
-      </c>
-      <c r="D29" t="s">
-        <v>1044</v>
-      </c>
-      <c r="E29" t="s">
-        <v>1045</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B29" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>1004</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>995</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>996</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <v>10000</v>
       </c>
-      <c r="B30" t="s">
-        <v>2102</v>
-      </c>
-      <c r="C30" t="s">
-        <v>848</v>
-      </c>
-      <c r="D30" t="s">
-        <v>1011</v>
-      </c>
-      <c r="E30" t="s">
-        <v>1012</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B30" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>1005</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>995</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>996</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <v>10000</v>
       </c>
-      <c r="B31" t="s">
-        <v>2102</v>
-      </c>
-      <c r="C31" t="s">
-        <v>1013</v>
-      </c>
-      <c r="D31" t="s">
-        <v>1014</v>
-      </c>
-      <c r="E31" t="s">
-        <v>1015</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B31" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>1006</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>995</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>996</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
         <v>10000</v>
       </c>
-      <c r="B32" t="s">
-        <v>2102</v>
-      </c>
-      <c r="C32" s="40" t="s">
-        <v>1040</v>
-      </c>
-      <c r="D32" s="40" t="s">
-        <v>1857</v>
-      </c>
-      <c r="E32" t="s">
-        <v>1858</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B32" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>1007</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>995</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>996</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
         <v>10000</v>
       </c>
-      <c r="B33" t="s">
-        <v>1020</v>
-      </c>
-      <c r="C33" t="s">
-        <v>1021</v>
-      </c>
-      <c r="D33" t="s">
-        <v>1022</v>
-      </c>
-      <c r="E33" t="s">
-        <v>1023</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B33" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>1008</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>995</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>996</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
         <v>10000</v>
       </c>
-      <c r="B34" t="s">
-        <v>1020</v>
-      </c>
-      <c r="C34" t="s">
-        <v>1024</v>
-      </c>
-      <c r="D34" t="s">
-        <v>1025</v>
-      </c>
-      <c r="E34" t="s">
-        <v>1026</v>
+      <c r="B34" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>1009</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>995</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>996</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
@@ -16216,7 +16219,7 @@
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A71" s="47">
+      <c r="A71" s="41">
         <v>14601</v>
       </c>
       <c r="B71" t="s">
@@ -16233,7 +16236,7 @@
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A72" s="47">
+      <c r="A72" s="41">
         <v>14601</v>
       </c>
       <c r="B72" t="s">
@@ -16250,7 +16253,7 @@
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A73" s="47">
+      <c r="A73" s="41">
         <v>14601</v>
       </c>
       <c r="B73" t="s">
@@ -16267,7 +16270,7 @@
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A74" s="47">
+      <c r="A74" s="41">
         <v>14601</v>
       </c>
       <c r="B74" t="s">
@@ -16284,7 +16287,7 @@
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A75" s="47">
+      <c r="A75" s="41">
         <v>14601</v>
       </c>
       <c r="B75" t="s">
@@ -16301,7 +16304,7 @@
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A76" s="47">
+      <c r="A76" s="41">
         <v>14601</v>
       </c>
       <c r="B76" t="s">
@@ -16318,7 +16321,7 @@
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A77" s="47">
+      <c r="A77" s="41">
         <v>14601</v>
       </c>
       <c r="B77" t="s">
@@ -16335,7 +16338,7 @@
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A78" s="47">
+      <c r="A78" s="41">
         <v>14601</v>
       </c>
       <c r="B78" t="s">
@@ -16352,7 +16355,7 @@
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A79" s="47">
+      <c r="A79" s="41">
         <v>14601</v>
       </c>
       <c r="B79" t="s">
@@ -16369,7 +16372,7 @@
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A80" s="47">
+      <c r="A80" s="41">
         <v>14601</v>
       </c>
       <c r="B80" t="s">
@@ -16386,7 +16389,7 @@
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A81" s="47">
+      <c r="A81" s="41">
         <v>14601</v>
       </c>
       <c r="B81" t="s">
@@ -16403,7 +16406,7 @@
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A82" s="47">
+      <c r="A82" s="41">
         <v>14601</v>
       </c>
       <c r="B82" t="s">
@@ -16420,7 +16423,7 @@
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A83" s="47">
+      <c r="A83" s="41">
         <v>14601</v>
       </c>
       <c r="B83" t="s">
@@ -16437,7 +16440,7 @@
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A84" s="47">
+      <c r="A84" s="41">
         <v>14601</v>
       </c>
       <c r="B84" t="s">
@@ -16454,7 +16457,7 @@
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A85" s="47">
+      <c r="A85" s="41">
         <v>14401</v>
       </c>
       <c r="B85" t="s">
@@ -16471,7 +16474,7 @@
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A86" s="47">
+      <c r="A86" s="41">
         <v>14401</v>
       </c>
       <c r="B86" t="s">
@@ -16488,7 +16491,7 @@
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A87" s="47">
+      <c r="A87" s="41">
         <v>14401</v>
       </c>
       <c r="B87" t="s">
@@ -16505,7 +16508,7 @@
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A88" s="47">
+      <c r="A88" s="41">
         <v>14401</v>
       </c>
       <c r="B88" t="s">
@@ -16522,7 +16525,7 @@
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A89" s="47">
+      <c r="A89" s="41">
         <v>14401</v>
       </c>
       <c r="B89" t="s">
@@ -16539,7 +16542,7 @@
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A90" s="47">
+      <c r="A90" s="41">
         <v>14401</v>
       </c>
       <c r="B90" t="s">
@@ -16556,7 +16559,7 @@
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A91" s="47">
+      <c r="A91" s="41">
         <v>14401</v>
       </c>
       <c r="B91" t="s">
@@ -16573,7 +16576,7 @@
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A92" s="47">
+      <c r="A92" s="41">
         <v>14401</v>
       </c>
       <c r="B92" t="s">
@@ -16590,7 +16593,7 @@
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A93" s="47">
+      <c r="A93" s="41">
         <v>14401</v>
       </c>
       <c r="B93" t="s">
@@ -16607,7 +16610,7 @@
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A94" s="47">
+      <c r="A94" s="41">
         <v>14401</v>
       </c>
       <c r="B94" t="s">
@@ -16624,7 +16627,7 @@
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A95" s="47">
+      <c r="A95" s="41">
         <v>14401</v>
       </c>
       <c r="B95" t="s">
@@ -16641,7 +16644,7 @@
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A96" s="47">
+      <c r="A96" s="41">
         <v>14401</v>
       </c>
       <c r="B96" t="s">
@@ -16658,7 +16661,7 @@
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A97" s="47">
+      <c r="A97" s="41">
         <v>14401</v>
       </c>
       <c r="B97" t="s">
@@ -16675,7 +16678,7 @@
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A98" s="47">
+      <c r="A98" s="41">
         <v>14401</v>
       </c>
       <c r="B98" t="s">
@@ -16692,7 +16695,7 @@
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A99" s="47">
+      <c r="A99" s="41">
         <v>14401</v>
       </c>
       <c r="B99" t="s">
@@ -16709,7 +16712,7 @@
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A100" s="47">
+      <c r="A100" s="41">
         <v>14401</v>
       </c>
       <c r="B100" t="s">
@@ -16726,7 +16729,7 @@
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A101" s="47">
+      <c r="A101" s="41">
         <v>14401</v>
       </c>
       <c r="B101" t="s">
@@ -16743,7 +16746,7 @@
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A102" s="47">
+      <c r="A102" s="41">
         <v>14401</v>
       </c>
       <c r="B102" t="s">
@@ -16760,7 +16763,7 @@
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A103" s="47">
+      <c r="A103" s="41">
         <v>14401</v>
       </c>
       <c r="B103" t="s">
@@ -16777,7 +16780,7 @@
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A104" s="47">
+      <c r="A104" s="41">
         <v>14401</v>
       </c>
       <c r="B104" t="s">
@@ -16794,7 +16797,7 @@
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A105" s="47">
+      <c r="A105" s="41">
         <v>14401</v>
       </c>
       <c r="B105" t="s">
@@ -16811,7 +16814,7 @@
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A106" s="47">
+      <c r="A106" s="41">
         <v>14401</v>
       </c>
       <c r="B106" t="s">
@@ -16828,7 +16831,7 @@
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A107" s="47">
+      <c r="A107" s="41">
         <v>14401</v>
       </c>
       <c r="B107" t="s">
@@ -16845,7 +16848,7 @@
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A108" s="47">
+      <c r="A108" s="41">
         <v>14401</v>
       </c>
       <c r="B108" t="s">
@@ -16862,7 +16865,7 @@
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A109" s="47">
+      <c r="A109" s="41">
         <v>14401</v>
       </c>
       <c r="B109" t="s">
@@ -16879,7 +16882,7 @@
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A110" s="47">
+      <c r="A110" s="41">
         <v>14401</v>
       </c>
       <c r="B110" t="s">
@@ -16896,7 +16899,7 @@
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A111" s="47">
+      <c r="A111" s="41">
         <v>14401</v>
       </c>
       <c r="B111" t="s">
@@ -16913,7 +16916,7 @@
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A112" s="47">
+      <c r="A112" s="41">
         <v>14403</v>
       </c>
       <c r="B112" t="s">
@@ -16930,7 +16933,7 @@
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A113" s="47">
+      <c r="A113" s="41">
         <v>14403</v>
       </c>
       <c r="B113" t="s">
@@ -16947,7 +16950,7 @@
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A114" s="47">
+      <c r="A114" s="41">
         <v>14403</v>
       </c>
       <c r="B114" t="s">
@@ -16964,7 +16967,7 @@
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A115" s="47">
+      <c r="A115" s="41">
         <v>14403</v>
       </c>
       <c r="B115" t="s">
@@ -16981,7 +16984,7 @@
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A116" s="47">
+      <c r="A116" s="41">
         <v>14403</v>
       </c>
       <c r="B116" t="s">
@@ -16998,7 +17001,7 @@
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A117" s="47">
+      <c r="A117" s="41">
         <v>14403</v>
       </c>
       <c r="B117" t="s">
@@ -17015,7 +17018,7 @@
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A118" s="47">
+      <c r="A118" s="41">
         <v>14403</v>
       </c>
       <c r="B118" t="s">
@@ -17032,7 +17035,7 @@
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A119" s="47">
+      <c r="A119" s="41">
         <v>14403</v>
       </c>
       <c r="B119" t="s">
@@ -17049,7 +17052,7 @@
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A120" s="47">
+      <c r="A120" s="41">
         <v>14303</v>
       </c>
       <c r="B120" t="s">
@@ -17066,7 +17069,7 @@
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A121" s="47">
+      <c r="A121" s="41">
         <v>14303</v>
       </c>
       <c r="B121" t="s">
@@ -17083,7 +17086,7 @@
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A122" s="47">
+      <c r="A122" s="41">
         <v>14303</v>
       </c>
       <c r="B122" t="s">
@@ -17100,7 +17103,7 @@
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A123" s="47">
+      <c r="A123" s="41">
         <v>14303</v>
       </c>
       <c r="B123" t="s">
@@ -17117,7 +17120,7 @@
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A124" s="47">
+      <c r="A124" s="41">
         <v>11201</v>
       </c>
       <c r="B124" t="s">
@@ -17134,7 +17137,7 @@
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A125" s="47">
+      <c r="A125" s="41">
         <v>11201</v>
       </c>
       <c r="B125" t="s">
@@ -17151,7 +17154,7 @@
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A126" s="47">
+      <c r="A126" s="41">
         <v>11201</v>
       </c>
       <c r="B126" t="s">
@@ -17168,7 +17171,7 @@
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A127" s="47">
+      <c r="A127" s="41">
         <v>11301</v>
       </c>
       <c r="B127" t="s">
@@ -17185,7 +17188,7 @@
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A128" s="47">
+      <c r="A128" s="41">
         <v>11301</v>
       </c>
       <c r="B128" t="s">
@@ -17202,7 +17205,7 @@
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A129" s="47">
+      <c r="A129" s="41">
         <v>11301</v>
       </c>
       <c r="B129" t="s">
@@ -17219,7 +17222,7 @@
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A130" s="47">
+      <c r="A130" s="41">
         <v>11301</v>
       </c>
       <c r="B130" t="s">
@@ -17236,7 +17239,7 @@
       </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A131" s="47">
+      <c r="A131" s="41">
         <v>11301</v>
       </c>
       <c r="B131" t="s">
@@ -17253,7 +17256,7 @@
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A132" s="47">
+      <c r="A132" s="41">
         <v>11301</v>
       </c>
       <c r="B132" t="s">
@@ -17270,7 +17273,7 @@
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A133" s="47">
+      <c r="A133" s="41">
         <v>11301</v>
       </c>
       <c r="B133" t="s">
@@ -17287,7 +17290,7 @@
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A134" s="47">
+      <c r="A134" s="41">
         <v>11301</v>
       </c>
       <c r="B134" t="s">
@@ -17304,7 +17307,7 @@
       </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A135" s="47">
+      <c r="A135" s="41">
         <v>11301</v>
       </c>
       <c r="B135" t="s">
@@ -17321,7 +17324,7 @@
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A136" s="47">
+      <c r="A136" s="41">
         <v>11301</v>
       </c>
       <c r="B136" t="s">
@@ -17338,7 +17341,7 @@
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A137" s="47">
+      <c r="A137" s="41">
         <v>11301</v>
       </c>
       <c r="B137" t="s">
@@ -17355,7 +17358,7 @@
       </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A138" s="47">
+      <c r="A138" s="41">
         <v>11301</v>
       </c>
       <c r="B138" t="s">
@@ -17372,7 +17375,7 @@
       </c>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A139" s="47">
+      <c r="A139" s="41">
         <v>11401</v>
       </c>
       <c r="B139" t="s">
@@ -17389,7 +17392,7 @@
       </c>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A140" s="47">
+      <c r="A140" s="41">
         <v>11401</v>
       </c>
       <c r="B140" t="s">
@@ -17406,7 +17409,7 @@
       </c>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A141" s="47">
+      <c r="A141" s="41">
         <v>11401</v>
       </c>
       <c r="B141" t="s">
@@ -17423,7 +17426,7 @@
       </c>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A142" s="47">
+      <c r="A142" s="41">
         <v>11401</v>
       </c>
       <c r="B142" t="s">
@@ -17440,7 +17443,7 @@
       </c>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A143" s="47">
+      <c r="A143" s="41">
         <v>11401</v>
       </c>
       <c r="B143" t="s">
@@ -17457,7 +17460,7 @@
       </c>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A144" s="47">
+      <c r="A144" s="41">
         <v>11401</v>
       </c>
       <c r="B144" t="s">
@@ -17474,7 +17477,7 @@
       </c>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A145" s="47">
+      <c r="A145" s="41">
         <v>11401</v>
       </c>
       <c r="B145" t="s">
@@ -17491,7 +17494,7 @@
       </c>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A146" s="47">
+      <c r="A146" s="41">
         <v>11401</v>
       </c>
       <c r="B146" t="s">
@@ -17508,7 +17511,7 @@
       </c>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A147" s="47">
+      <c r="A147" s="41">
         <v>11401</v>
       </c>
       <c r="B147" t="s">
@@ -17525,7 +17528,7 @@
       </c>
     </row>
     <row r="148" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A148" s="47">
+      <c r="A148" s="41">
         <v>11401</v>
       </c>
       <c r="B148" t="s">
@@ -17542,7 +17545,7 @@
       </c>
     </row>
     <row r="149" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A149" s="47">
+      <c r="A149" s="41">
         <v>11501</v>
       </c>
       <c r="B149" t="s">
@@ -17559,7 +17562,7 @@
       </c>
     </row>
     <row r="150" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A150" s="47">
+      <c r="A150" s="41">
         <v>11501</v>
       </c>
       <c r="B150" t="s">
@@ -17576,7 +17579,7 @@
       </c>
     </row>
     <row r="151" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A151" s="47">
+      <c r="A151" s="41">
         <v>11501</v>
       </c>
       <c r="B151" t="s">
@@ -17593,7 +17596,7 @@
       </c>
     </row>
     <row r="152" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A152" s="47">
+      <c r="A152" s="41">
         <v>11501</v>
       </c>
       <c r="B152" t="s">
@@ -17610,7 +17613,7 @@
       </c>
     </row>
     <row r="153" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A153" s="47">
+      <c r="A153" s="41">
         <v>11501</v>
       </c>
       <c r="B153" t="s">
@@ -17627,7 +17630,7 @@
       </c>
     </row>
     <row r="154" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A154" s="47">
+      <c r="A154" s="41">
         <v>11501</v>
       </c>
       <c r="B154" t="s">
@@ -17644,7 +17647,7 @@
       </c>
     </row>
     <row r="155" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A155" s="47">
+      <c r="A155" s="41">
         <v>11501</v>
       </c>
       <c r="B155" t="s">
@@ -17661,7 +17664,7 @@
       </c>
     </row>
     <row r="156" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A156" s="47">
+      <c r="A156" s="41">
         <v>11501</v>
       </c>
       <c r="B156" t="s">
@@ -17678,7 +17681,7 @@
       </c>
     </row>
     <row r="157" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A157" s="47">
+      <c r="A157" s="41">
         <v>11501</v>
       </c>
       <c r="B157" t="s">
@@ -17695,7 +17698,7 @@
       </c>
     </row>
     <row r="158" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A158" s="47">
+      <c r="A158" s="41">
         <v>11501</v>
       </c>
       <c r="B158" t="s">
@@ -17712,7 +17715,7 @@
       </c>
     </row>
     <row r="159" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A159" s="47">
+      <c r="A159" s="41">
         <v>11501</v>
       </c>
       <c r="B159" t="s">
@@ -17729,7 +17732,7 @@
       </c>
     </row>
     <row r="160" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A160" s="47">
+      <c r="A160" s="41">
         <v>11501</v>
       </c>
       <c r="B160" t="s">
@@ -17746,7 +17749,7 @@
       </c>
     </row>
     <row r="161" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A161" s="47">
+      <c r="A161" s="41">
         <v>11501</v>
       </c>
       <c r="B161" t="s">
@@ -17763,7 +17766,7 @@
       </c>
     </row>
     <row r="162" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A162" s="47">
+      <c r="A162" s="41">
         <v>11501</v>
       </c>
       <c r="B162" t="s">
@@ -17780,7 +17783,7 @@
       </c>
     </row>
     <row r="163" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A163" s="47">
+      <c r="A163" s="41">
         <v>11501</v>
       </c>
       <c r="B163" t="s">
@@ -17797,7 +17800,7 @@
       </c>
     </row>
     <row r="164" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A164" s="47">
+      <c r="A164" s="41">
         <v>11501</v>
       </c>
       <c r="B164" t="s">
@@ -17814,7 +17817,7 @@
       </c>
     </row>
     <row r="165" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A165" s="47">
+      <c r="A165" s="41">
         <v>11501</v>
       </c>
       <c r="B165" t="s">
@@ -17831,7 +17834,7 @@
       </c>
     </row>
     <row r="166" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A166" s="47">
+      <c r="A166" s="41">
         <v>11501</v>
       </c>
       <c r="B166" t="s">
@@ -17848,7 +17851,7 @@
       </c>
     </row>
     <row r="167" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A167" s="47">
+      <c r="A167" s="41">
         <v>11501</v>
       </c>
       <c r="B167" t="s">
@@ -17865,7 +17868,7 @@
       </c>
     </row>
     <row r="168" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A168" s="47">
+      <c r="A168" s="41">
         <v>11502</v>
       </c>
       <c r="B168" t="s">
@@ -17882,7 +17885,7 @@
       </c>
     </row>
     <row r="169" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A169" s="47">
+      <c r="A169" s="41">
         <v>11502</v>
       </c>
       <c r="B169" t="s">
@@ -17899,7 +17902,7 @@
       </c>
     </row>
     <row r="170" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A170" s="47">
+      <c r="A170" s="41">
         <v>11502</v>
       </c>
       <c r="B170" t="s">
@@ -17916,7 +17919,7 @@
       </c>
     </row>
     <row r="171" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A171" s="47">
+      <c r="A171" s="41">
         <v>11502</v>
       </c>
       <c r="B171" t="s">
@@ -17933,7 +17936,7 @@
       </c>
     </row>
     <row r="172" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A172" s="47">
+      <c r="A172" s="41">
         <v>11502</v>
       </c>
       <c r="B172" t="s">
@@ -17950,7 +17953,7 @@
       </c>
     </row>
     <row r="173" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A173" s="47">
+      <c r="A173" s="41">
         <v>11502</v>
       </c>
       <c r="B173" t="s">
@@ -17967,7 +17970,7 @@
       </c>
     </row>
     <row r="174" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A174" s="47">
+      <c r="A174" s="41">
         <v>11502</v>
       </c>
       <c r="B174" t="s">
@@ -17984,7 +17987,7 @@
       </c>
     </row>
     <row r="175" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A175" s="47">
+      <c r="A175" s="41">
         <v>11502</v>
       </c>
       <c r="B175" t="s">
@@ -18001,7 +18004,7 @@
       </c>
     </row>
     <row r="176" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A176" s="47">
+      <c r="A176" s="41">
         <v>11502</v>
       </c>
       <c r="B176" t="s">
@@ -18018,7 +18021,7 @@
       </c>
     </row>
     <row r="177" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A177" s="47">
+      <c r="A177" s="41">
         <v>11502</v>
       </c>
       <c r="B177" t="s">
@@ -18035,7 +18038,7 @@
       </c>
     </row>
     <row r="178" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A178" s="47">
+      <c r="A178" s="41">
         <v>12201</v>
       </c>
       <c r="B178" t="s">
@@ -18052,7 +18055,7 @@
       </c>
     </row>
     <row r="179" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A179" s="47">
+      <c r="A179" s="41">
         <v>12201</v>
       </c>
       <c r="B179" t="s">
@@ -18069,7 +18072,7 @@
       </c>
     </row>
     <row r="180" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A180" s="47">
+      <c r="A180" s="41">
         <v>12201</v>
       </c>
       <c r="B180" t="s">
@@ -18086,7 +18089,7 @@
       </c>
     </row>
     <row r="181" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A181" s="47">
+      <c r="A181" s="41">
         <v>12201</v>
       </c>
       <c r="B181" t="s">
@@ -18103,7 +18106,7 @@
       </c>
     </row>
     <row r="182" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A182" s="47">
+      <c r="A182" s="41">
         <v>12201</v>
       </c>
       <c r="B182" t="s">
@@ -18120,7 +18123,7 @@
       </c>
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A183" s="47">
+      <c r="A183" s="41">
         <v>12201</v>
       </c>
       <c r="B183" t="s">
@@ -18137,7 +18140,7 @@
       </c>
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A184" s="47">
+      <c r="A184" s="41">
         <v>12201</v>
       </c>
       <c r="B184" t="s">
@@ -18154,7 +18157,7 @@
       </c>
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A185" s="47">
+      <c r="A185" s="41">
         <v>12201</v>
       </c>
       <c r="B185" t="s">
@@ -18171,7 +18174,7 @@
       </c>
     </row>
     <row r="186" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A186" s="47">
+      <c r="A186" s="41">
         <v>12201</v>
       </c>
       <c r="B186" t="s">
@@ -18188,7 +18191,7 @@
       </c>
     </row>
     <row r="187" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A187" s="47">
+      <c r="A187" s="41">
         <v>12201</v>
       </c>
       <c r="B187" t="s">
@@ -18205,7 +18208,7 @@
       </c>
     </row>
     <row r="188" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A188" s="47">
+      <c r="A188" s="41">
         <v>12201</v>
       </c>
       <c r="B188" t="s">
@@ -18222,7 +18225,7 @@
       </c>
     </row>
     <row r="189" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A189" s="47">
+      <c r="A189" s="41">
         <v>12201</v>
       </c>
       <c r="B189" t="s">
@@ -18239,7 +18242,7 @@
       </c>
     </row>
     <row r="190" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A190" s="47">
+      <c r="A190" s="41">
         <v>12201</v>
       </c>
       <c r="B190" t="s">
@@ -18256,7 +18259,7 @@
       </c>
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A191" s="47">
+      <c r="A191" s="41">
         <v>12201</v>
       </c>
       <c r="B191" t="s">
@@ -18273,7 +18276,7 @@
       </c>
     </row>
     <row r="192" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A192" s="47">
+      <c r="A192" s="41">
         <v>12201</v>
       </c>
       <c r="B192" t="s">
@@ -18290,7 +18293,7 @@
       </c>
     </row>
     <row r="193" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A193" s="47">
+      <c r="A193" s="41">
         <v>12201</v>
       </c>
       <c r="B193" t="s">
@@ -18307,7 +18310,7 @@
       </c>
     </row>
     <row r="194" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A194" s="47">
+      <c r="A194" s="41">
         <v>12201</v>
       </c>
       <c r="B194" t="s">
@@ -18324,7 +18327,7 @@
       </c>
     </row>
     <row r="195" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A195" s="47">
+      <c r="A195" s="41">
         <v>12201</v>
       </c>
       <c r="B195" t="s">
@@ -18341,7 +18344,7 @@
       </c>
     </row>
     <row r="196" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A196" s="47">
+      <c r="A196" s="41">
         <v>12303</v>
       </c>
       <c r="B196" t="s">
@@ -18358,7 +18361,7 @@
       </c>
     </row>
     <row r="197" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A197" s="47">
+      <c r="A197" s="41">
         <v>12303</v>
       </c>
       <c r="B197" t="s">
@@ -18375,7 +18378,7 @@
       </c>
     </row>
     <row r="198" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A198" s="47">
+      <c r="A198" s="41">
         <v>12303</v>
       </c>
       <c r="B198" t="s">
@@ -18392,7 +18395,7 @@
       </c>
     </row>
     <row r="199" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A199" s="47">
+      <c r="A199" s="41">
         <v>12303</v>
       </c>
       <c r="B199" t="s">
@@ -18409,7 +18412,7 @@
       </c>
     </row>
     <row r="200" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A200" s="47">
+      <c r="A200" s="41">
         <v>12303</v>
       </c>
       <c r="B200" t="s">
@@ -18426,7 +18429,7 @@
       </c>
     </row>
     <row r="201" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A201" s="47">
+      <c r="A201" s="41">
         <v>12303</v>
       </c>
       <c r="B201" t="s">
@@ -18443,7 +18446,7 @@
       </c>
     </row>
     <row r="202" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A202" s="47">
+      <c r="A202" s="41">
         <v>12303</v>
       </c>
       <c r="B202" t="s">
@@ -18460,7 +18463,7 @@
       </c>
     </row>
     <row r="203" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A203" s="47">
+      <c r="A203" s="41">
         <v>12303</v>
       </c>
       <c r="B203" t="s">
@@ -18477,7 +18480,7 @@
       </c>
     </row>
     <row r="204" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A204" s="47">
+      <c r="A204" s="41">
         <v>12303</v>
       </c>
       <c r="B204" t="s">
@@ -18494,7 +18497,7 @@
       </c>
     </row>
     <row r="205" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A205" s="47">
+      <c r="A205" s="41">
         <v>13101</v>
       </c>
       <c r="B205" t="s">
@@ -18508,7 +18511,7 @@
       </c>
     </row>
     <row r="206" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A206" s="47">
+      <c r="A206" s="41">
         <v>13101</v>
       </c>
       <c r="B206" t="s">
@@ -18522,7 +18525,7 @@
       </c>
     </row>
     <row r="207" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A207" s="47">
+      <c r="A207" s="41">
         <v>13101</v>
       </c>
       <c r="B207" t="s">
@@ -18536,7 +18539,7 @@
       </c>
     </row>
     <row r="208" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A208" s="47">
+      <c r="A208" s="41">
         <v>13101</v>
       </c>
       <c r="B208" t="s">
@@ -18550,7 +18553,7 @@
       </c>
     </row>
     <row r="209" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A209" s="47">
+      <c r="A209" s="41">
         <v>13101</v>
       </c>
       <c r="B209" t="s">
@@ -18564,7 +18567,7 @@
       </c>
     </row>
     <row r="210" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A210" s="47">
+      <c r="A210" s="41">
         <v>13101</v>
       </c>
       <c r="B210" t="s">
@@ -18578,7 +18581,7 @@
       </c>
     </row>
     <row r="211" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A211" s="47">
+      <c r="A211" s="41">
         <v>13101</v>
       </c>
       <c r="B211" t="s">
@@ -18592,7 +18595,7 @@
       </c>
     </row>
     <row r="212" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A212" s="47">
+      <c r="A212" s="41">
         <v>13101</v>
       </c>
       <c r="B212" t="s">
@@ -18606,7 +18609,7 @@
       </c>
     </row>
     <row r="213" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A213" s="47">
+      <c r="A213" s="41">
         <v>13101</v>
       </c>
       <c r="B213" t="s">
@@ -18620,7 +18623,7 @@
       </c>
     </row>
     <row r="214" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A214" s="47">
+      <c r="A214" s="41">
         <v>13101</v>
       </c>
       <c r="B214" t="s">
@@ -18634,7 +18637,7 @@
       </c>
     </row>
     <row r="215" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A215" s="47">
+      <c r="A215" s="41">
         <v>13101</v>
       </c>
       <c r="B215" t="s">
@@ -18648,7 +18651,7 @@
       </c>
     </row>
     <row r="216" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A216" s="47">
+      <c r="A216" s="41">
         <v>13101</v>
       </c>
       <c r="B216" t="s">
@@ -18662,7 +18665,7 @@
       </c>
     </row>
     <row r="217" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A217" s="47">
+      <c r="A217" s="41">
         <v>13101</v>
       </c>
       <c r="B217" t="s">
@@ -18676,7 +18679,7 @@
       </c>
     </row>
     <row r="218" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A218" s="47">
+      <c r="A218" s="41">
         <v>13101</v>
       </c>
       <c r="B218" t="s">
@@ -18690,7 +18693,7 @@
       </c>
     </row>
     <row r="219" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A219" s="47">
+      <c r="A219" s="41">
         <v>13101</v>
       </c>
       <c r="B219" t="s">
@@ -18704,7 +18707,7 @@
       </c>
     </row>
     <row r="220" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A220" s="47">
+      <c r="A220" s="41">
         <v>13101</v>
       </c>
       <c r="B220" t="s">
@@ -18718,7 +18721,7 @@
       </c>
     </row>
     <row r="221" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A221" s="47">
+      <c r="A221" s="41">
         <v>13104</v>
       </c>
       <c r="B221" t="s">
@@ -18732,7 +18735,7 @@
       </c>
     </row>
     <row r="222" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A222" s="47">
+      <c r="A222" s="41">
         <v>13104</v>
       </c>
       <c r="B222" t="s">
@@ -18746,7 +18749,7 @@
       </c>
     </row>
     <row r="223" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A223" s="47">
+      <c r="A223" s="41">
         <v>13104</v>
       </c>
       <c r="B223" t="s">
@@ -18760,7 +18763,7 @@
       </c>
     </row>
     <row r="224" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A224" s="47">
+      <c r="A224" s="41">
         <v>13104</v>
       </c>
       <c r="B224" t="s">
@@ -18774,7 +18777,7 @@
       </c>
     </row>
     <row r="225" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A225" s="47">
+      <c r="A225" s="41">
         <v>13104</v>
       </c>
       <c r="B225" t="s">
@@ -18788,7 +18791,7 @@
       </c>
     </row>
     <row r="226" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A226" s="47">
+      <c r="A226" s="41">
         <v>13104</v>
       </c>
       <c r="B226" t="s">
@@ -18802,7 +18805,7 @@
       </c>
     </row>
     <row r="227" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A227" s="47">
+      <c r="A227" s="41">
         <v>13104</v>
       </c>
       <c r="B227" t="s">
@@ -18884,7 +18887,7 @@
       </c>
     </row>
     <row r="232" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A232" s="47" t="s">
+      <c r="A232" s="41" t="s">
         <v>2170</v>
       </c>
       <c r="B232" t="s">
@@ -18901,7 +18904,7 @@
       </c>
     </row>
     <row r="233" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A233" s="47" t="s">
+      <c r="A233" s="41" t="s">
         <v>2170</v>
       </c>
       <c r="B233" t="s">
@@ -18918,7 +18921,7 @@
       </c>
     </row>
     <row r="234" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A234" s="47" t="s">
+      <c r="A234" s="41" t="s">
         <v>2170</v>
       </c>
       <c r="B234" t="s">
@@ -18935,7 +18938,7 @@
       </c>
     </row>
     <row r="235" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A235" s="47" t="s">
+      <c r="A235" s="41" t="s">
         <v>2170</v>
       </c>
       <c r="B235" t="s">
@@ -18952,7 +18955,7 @@
       </c>
     </row>
     <row r="236" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A236" s="47" t="s">
+      <c r="A236" s="41" t="s">
         <v>2170</v>
       </c>
       <c r="B236" t="s">
@@ -18969,7 +18972,7 @@
       </c>
     </row>
     <row r="237" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A237" s="47" t="s">
+      <c r="A237" s="41" t="s">
         <v>2170</v>
       </c>
       <c r="B237" t="s">
@@ -18986,7 +18989,7 @@
       </c>
     </row>
     <row r="238" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A238" s="47" t="s">
+      <c r="A238" s="41" t="s">
         <v>2170</v>
       </c>
       <c r="B238" t="s">
@@ -19003,7 +19006,7 @@
       </c>
     </row>
     <row r="239" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A239" s="47" t="s">
+      <c r="A239" s="41" t="s">
         <v>2170</v>
       </c>
       <c r="B239" t="s">
@@ -19020,7 +19023,7 @@
       </c>
     </row>
     <row r="240" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A240" s="47" t="s">
+      <c r="A240" s="41" t="s">
         <v>2170</v>
       </c>
       <c r="B240" t="s">
@@ -19037,7 +19040,7 @@
       </c>
     </row>
     <row r="241" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A241" s="47" t="s">
+      <c r="A241" s="41" t="s">
         <v>2170</v>
       </c>
       <c r="B241" t="s">
@@ -19054,7 +19057,7 @@
       </c>
     </row>
     <row r="242" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A242" s="47" t="s">
+      <c r="A242" s="41" t="s">
         <v>2170</v>
       </c>
       <c r="B242" t="s">
@@ -19071,7 +19074,7 @@
       </c>
     </row>
     <row r="243" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A243" s="47" t="s">
+      <c r="A243" s="41" t="s">
         <v>2170</v>
       </c>
       <c r="B243" t="s">
@@ -19088,7 +19091,7 @@
       </c>
     </row>
     <row r="244" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A244" s="47" t="s">
+      <c r="A244" s="41" t="s">
         <v>2170</v>
       </c>
       <c r="B244" t="s">
@@ -19105,7 +19108,7 @@
       </c>
     </row>
     <row r="245" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A245" s="47" t="s">
+      <c r="A245" s="41" t="s">
         <v>2170</v>
       </c>
       <c r="B245" t="s">
@@ -19122,7 +19125,7 @@
       </c>
     </row>
     <row r="246" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A246" s="47" t="s">
+      <c r="A246" s="41" t="s">
         <v>2170</v>
       </c>
       <c r="B246" t="s">
@@ -19139,7 +19142,7 @@
       </c>
     </row>
     <row r="247" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A247" s="47" t="s">
+      <c r="A247" s="41" t="s">
         <v>2170</v>
       </c>
       <c r="B247" t="s">
@@ -19156,7 +19159,7 @@
       </c>
     </row>
     <row r="248" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A248" s="47" t="s">
+      <c r="A248" s="41" t="s">
         <v>2170</v>
       </c>
       <c r="B248" t="s">
@@ -19173,7 +19176,7 @@
       </c>
     </row>
     <row r="249" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A249" s="47" t="s">
+      <c r="A249" s="41" t="s">
         <v>2170</v>
       </c>
       <c r="B249" t="s">
@@ -19190,7 +19193,7 @@
       </c>
     </row>
     <row r="250" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A250" s="47" t="s">
+      <c r="A250" s="41" t="s">
         <v>2170</v>
       </c>
       <c r="B250" t="s">
@@ -19207,7 +19210,7 @@
       </c>
     </row>
     <row r="251" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A251" s="47" t="s">
+      <c r="A251" s="41" t="s">
         <v>2153</v>
       </c>
       <c r="B251" t="s">
@@ -19224,7 +19227,7 @@
       </c>
     </row>
     <row r="252" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A252" s="47" t="s">
+      <c r="A252" s="41" t="s">
         <v>2153</v>
       </c>
       <c r="B252" t="s">
@@ -19241,7 +19244,7 @@
       </c>
     </row>
     <row r="253" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A253" s="47" t="s">
+      <c r="A253" s="41" t="s">
         <v>2153</v>
       </c>
       <c r="B253" t="s">
@@ -19258,7 +19261,7 @@
       </c>
     </row>
     <row r="254" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A254" s="47" t="s">
+      <c r="A254" s="41" t="s">
         <v>2153</v>
       </c>
       <c r="B254" t="s">
@@ -19275,7 +19278,7 @@
       </c>
     </row>
     <row r="255" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A255" s="47" t="s">
+      <c r="A255" s="41" t="s">
         <v>2153</v>
       </c>
       <c r="B255" t="s">
@@ -19292,7 +19295,7 @@
       </c>
     </row>
     <row r="256" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A256" s="47" t="s">
+      <c r="A256" s="41" t="s">
         <v>2153</v>
       </c>
       <c r="B256" t="s">
@@ -19309,7 +19312,7 @@
       </c>
     </row>
     <row r="257" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A257" s="47" t="s">
+      <c r="A257" s="41" t="s">
         <v>2153</v>
       </c>
       <c r="B257" t="s">
@@ -19326,7 +19329,7 @@
       </c>
     </row>
     <row r="258" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A258" s="47" t="s">
+      <c r="A258" s="41" t="s">
         <v>2153</v>
       </c>
       <c r="B258" t="s">
@@ -19343,7 +19346,7 @@
       </c>
     </row>
     <row r="259" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A259" s="47" t="s">
+      <c r="A259" s="41" t="s">
         <v>2153</v>
       </c>
       <c r="B259" t="s">
@@ -19360,7 +19363,7 @@
       </c>
     </row>
     <row r="260" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A260" s="47" t="s">
+      <c r="A260" s="41" t="s">
         <v>2153</v>
       </c>
       <c r="B260" t="s">
@@ -19377,7 +19380,7 @@
       </c>
     </row>
     <row r="261" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A261" s="47" t="s">
+      <c r="A261" s="41" t="s">
         <v>2153</v>
       </c>
       <c r="B261" t="s">
@@ -19394,7 +19397,7 @@
       </c>
     </row>
     <row r="262" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A262" s="47">
+      <c r="A262" s="41">
         <v>12003</v>
       </c>
       <c r="B262" t="s">
@@ -19411,7 +19414,7 @@
       </c>
     </row>
     <row r="263" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A263" s="47">
+      <c r="A263" s="41">
         <v>12003</v>
       </c>
       <c r="B263" t="s">
@@ -19428,7 +19431,7 @@
       </c>
     </row>
     <row r="264" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A264" s="47">
+      <c r="A264" s="41">
         <v>12003</v>
       </c>
       <c r="B264" t="s">
@@ -19445,7 +19448,7 @@
       </c>
     </row>
     <row r="265" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A265" s="47">
+      <c r="A265" s="41">
         <v>12003</v>
       </c>
       <c r="B265" t="s">
@@ -19462,7 +19465,7 @@
       </c>
     </row>
     <row r="266" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A266" s="47">
+      <c r="A266" s="41">
         <v>12003</v>
       </c>
       <c r="B266" t="s">
@@ -19479,7 +19482,7 @@
       </c>
     </row>
     <row r="267" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A267" s="47">
+      <c r="A267" s="41">
         <v>12003</v>
       </c>
       <c r="B267" t="s">
@@ -19601,7 +19604,7 @@
       <c r="E274" s="7"/>
     </row>
     <row r="275" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A275" s="47">
+      <c r="A275" s="41">
         <v>11701</v>
       </c>
       <c r="B275" t="s">
@@ -19618,7 +19621,7 @@
       </c>
     </row>
     <row r="276" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A276" s="47">
+      <c r="A276" s="41">
         <v>11701</v>
       </c>
       <c r="B276" t="s">
@@ -19635,7 +19638,7 @@
       </c>
     </row>
     <row r="277" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A277" s="47">
+      <c r="A277" s="41">
         <v>11701</v>
       </c>
       <c r="B277" t="s">
@@ -19652,7 +19655,7 @@
       </c>
     </row>
     <row r="278" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A278" s="47">
+      <c r="A278" s="41">
         <v>11701</v>
       </c>
       <c r="B278" t="s">
@@ -19669,7 +19672,7 @@
       </c>
     </row>
     <row r="279" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A279" s="47">
+      <c r="A279" s="41">
         <v>11701</v>
       </c>
       <c r="B279" t="s">
@@ -19686,7 +19689,7 @@
       </c>
     </row>
     <row r="280" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A280" s="47">
+      <c r="A280" s="41">
         <v>12601</v>
       </c>
       <c r="B280" t="s">
@@ -19703,7 +19706,7 @@
       </c>
     </row>
     <row r="281" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A281" s="47">
+      <c r="A281" s="41">
         <v>12601</v>
       </c>
       <c r="B281" t="s">
@@ -19720,7 +19723,7 @@
       </c>
     </row>
     <row r="282" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A282" s="47">
+      <c r="A282" s="41">
         <v>12601</v>
       </c>
       <c r="B282" t="s">
@@ -19737,7 +19740,7 @@
       </c>
     </row>
     <row r="283" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A283" s="47">
+      <c r="A283" s="41">
         <v>12601</v>
       </c>
       <c r="B283" t="s">
@@ -19754,7 +19757,7 @@
       </c>
     </row>
     <row r="284" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A284" s="47">
+      <c r="A284" s="41">
         <v>12601</v>
       </c>
       <c r="B284" t="s">
@@ -19771,7 +19774,7 @@
       </c>
     </row>
     <row r="285" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A285" s="47">
+      <c r="A285" s="41">
         <v>12601</v>
       </c>
       <c r="B285" t="s">
@@ -19788,7 +19791,7 @@
       </c>
     </row>
     <row r="286" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A286" s="47">
+      <c r="A286" s="41">
         <v>12601</v>
       </c>
       <c r="B286" t="s">
@@ -19805,7 +19808,7 @@
       </c>
     </row>
     <row r="287" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A287" s="47">
+      <c r="A287" s="41">
         <v>12601</v>
       </c>
       <c r="B287" t="s">
@@ -19822,7 +19825,7 @@
       </c>
     </row>
     <row r="288" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A288" s="47">
+      <c r="A288" s="41">
         <v>12601</v>
       </c>
       <c r="B288" t="s">
@@ -19839,7 +19842,7 @@
       </c>
     </row>
     <row r="289" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A289" s="47">
+      <c r="A289" s="41">
         <v>12601</v>
       </c>
       <c r="B289" t="s">
@@ -19856,7 +19859,7 @@
       </c>
     </row>
     <row r="290" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A290" s="47">
+      <c r="A290" s="41">
         <v>12601</v>
       </c>
       <c r="B290" t="s">
@@ -19873,7 +19876,7 @@
       </c>
     </row>
     <row r="291" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A291" s="47">
+      <c r="A291" s="41">
         <v>12601</v>
       </c>
       <c r="B291" t="s">
@@ -19890,7 +19893,7 @@
       </c>
     </row>
     <row r="292" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A292" s="47">
+      <c r="A292" s="41">
         <v>12601</v>
       </c>
       <c r="B292" t="s">
@@ -19907,7 +19910,7 @@
       </c>
     </row>
     <row r="293" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A293" s="47">
+      <c r="A293" s="41">
         <v>11101</v>
       </c>
       <c r="B293" t="s">
@@ -19924,7 +19927,7 @@
       </c>
     </row>
     <row r="294" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A294" s="47">
+      <c r="A294" s="41">
         <v>11101</v>
       </c>
       <c r="B294" t="s">
@@ -19941,7 +19944,7 @@
       </c>
     </row>
     <row r="295" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A295" s="47">
+      <c r="A295" s="41">
         <v>11101</v>
       </c>
       <c r="B295" t="s">
@@ -19958,7 +19961,7 @@
       </c>
     </row>
     <row r="296" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A296" s="47">
+      <c r="A296" s="41">
         <v>11101</v>
       </c>
       <c r="B296" t="s">
@@ -19975,7 +19978,7 @@
       </c>
     </row>
     <row r="297" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A297" s="47">
+      <c r="A297" s="41">
         <v>11101</v>
       </c>
       <c r="B297" t="s">
@@ -19992,7 +19995,7 @@
       </c>
     </row>
     <row r="298" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A298" s="47">
+      <c r="A298" s="41">
         <v>10901</v>
       </c>
       <c r="B298" t="s">
@@ -20009,7 +20012,7 @@
       </c>
     </row>
     <row r="299" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A299" s="47">
+      <c r="A299" s="41">
         <v>10901</v>
       </c>
       <c r="B299" t="s">
@@ -20026,7 +20029,7 @@
       </c>
     </row>
     <row r="300" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A300" s="47">
+      <c r="A300" s="41">
         <v>10901</v>
       </c>
       <c r="B300" t="s">
@@ -20043,7 +20046,7 @@
       </c>
     </row>
     <row r="301" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A301" s="47">
+      <c r="A301" s="41">
         <v>10901</v>
       </c>
       <c r="B301" t="s">
@@ -20060,7 +20063,7 @@
       </c>
     </row>
     <row r="302" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A302" s="47">
+      <c r="A302" s="41">
         <v>10901</v>
       </c>
       <c r="B302" t="s">
@@ -20077,7 +20080,7 @@
       </c>
     </row>
     <row r="303" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A303" s="47">
+      <c r="A303" s="41">
         <v>12501</v>
       </c>
       <c r="B303" t="s">
@@ -20094,7 +20097,7 @@
       </c>
     </row>
     <row r="304" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A304" s="47">
+      <c r="A304" s="41">
         <v>12501</v>
       </c>
       <c r="B304" t="s">
@@ -20111,7 +20114,7 @@
       </c>
     </row>
     <row r="305" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A305" s="47">
+      <c r="A305" s="41">
         <v>12501</v>
       </c>
       <c r="B305" t="s">
@@ -20128,7 +20131,7 @@
       </c>
     </row>
     <row r="306" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A306" s="47">
+      <c r="A306" s="41">
         <v>12501</v>
       </c>
       <c r="B306" t="s">
@@ -20145,7 +20148,7 @@
       </c>
     </row>
     <row r="307" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A307" s="47">
+      <c r="A307" s="41">
         <v>12501</v>
       </c>
       <c r="B307" t="s">
@@ -20162,7 +20165,7 @@
       </c>
     </row>
     <row r="308" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A308" s="47">
+      <c r="A308" s="41">
         <v>12501</v>
       </c>
       <c r="B308" t="s">
@@ -20179,7 +20182,7 @@
       </c>
     </row>
     <row r="309" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A309" s="47">
+      <c r="A309" s="41">
         <v>12501</v>
       </c>
       <c r="B309" t="s">
@@ -20196,7 +20199,7 @@
       </c>
     </row>
     <row r="310" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A310" s="47">
+      <c r="A310" s="41">
         <v>12501</v>
       </c>
       <c r="B310" t="s">
@@ -20213,7 +20216,7 @@
       </c>
     </row>
     <row r="311" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A311" s="47">
+      <c r="A311" s="41">
         <v>12501</v>
       </c>
       <c r="B311" t="s">
@@ -20230,7 +20233,7 @@
       </c>
     </row>
     <row r="312" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A312" s="47">
+      <c r="A312" s="41">
         <v>12502</v>
       </c>
       <c r="B312" t="s">
@@ -20247,7 +20250,7 @@
       </c>
     </row>
     <row r="313" spans="1:5" s="29" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A313" s="47">
+      <c r="A313" s="41">
         <v>12502</v>
       </c>
       <c r="B313" s="29" t="s">
@@ -20264,7 +20267,7 @@
       </c>
     </row>
     <row r="314" spans="1:5" s="29" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A314" s="47">
+      <c r="A314" s="41">
         <v>12502</v>
       </c>
       <c r="B314" s="29" t="s">
@@ -20281,7 +20284,7 @@
       </c>
     </row>
     <row r="315" spans="1:5" s="29" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A315" s="47">
+      <c r="A315" s="41">
         <v>12502</v>
       </c>
       <c r="B315" s="29" t="s">
@@ -20298,7 +20301,7 @@
       </c>
     </row>
     <row r="316" spans="1:5" s="29" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A316" s="47">
+      <c r="A316" s="41">
         <v>12502</v>
       </c>
       <c r="B316" s="29" t="s">
@@ -20315,7 +20318,7 @@
       </c>
     </row>
     <row r="317" spans="1:5" s="29" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A317" s="47">
+      <c r="A317" s="41">
         <v>12502</v>
       </c>
       <c r="B317" s="29" t="s">
@@ -20332,7 +20335,7 @@
       </c>
     </row>
     <row r="318" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A318" s="47">
+      <c r="A318" s="41">
         <v>12502</v>
       </c>
       <c r="B318" t="s">
@@ -20349,7 +20352,7 @@
       </c>
     </row>
     <row r="319" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A319" s="47">
+      <c r="A319" s="41">
         <v>12502</v>
       </c>
       <c r="B319" t="s">
@@ -20366,7 +20369,7 @@
       </c>
     </row>
     <row r="320" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A320" s="47">
+      <c r="A320" s="41">
         <v>12502</v>
       </c>
       <c r="B320" s="30" t="s">
@@ -20383,7 +20386,7 @@
       </c>
     </row>
     <row r="321" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A321" s="47">
+      <c r="A321" s="41">
         <v>12502</v>
       </c>
       <c r="B321" s="30" t="s">
@@ -20400,7 +20403,7 @@
       </c>
     </row>
     <row r="322" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A322" s="47">
+      <c r="A322" s="41">
         <v>12502</v>
       </c>
       <c r="B322" t="s">
@@ -20417,7 +20420,7 @@
       </c>
     </row>
     <row r="323" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A323" s="47">
+      <c r="A323" s="41">
         <v>12502</v>
       </c>
       <c r="B323" t="s">
@@ -20434,7 +20437,7 @@
       </c>
     </row>
     <row r="324" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A324" s="47">
+      <c r="A324" s="41">
         <v>12502</v>
       </c>
       <c r="B324" t="s">
@@ -20451,7 +20454,7 @@
       </c>
     </row>
     <row r="325" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A325" s="47">
+      <c r="A325" s="41">
         <v>12502</v>
       </c>
       <c r="B325" t="s">
@@ -20468,7 +20471,7 @@
       </c>
     </row>
     <row r="326" spans="1:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A326" s="47">
+      <c r="A326" s="41">
         <v>12502</v>
       </c>
       <c r="B326" s="29" t="s">
@@ -20485,7 +20488,7 @@
       </c>
     </row>
     <row r="327" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A327" s="47">
+      <c r="A327" s="41">
         <v>12502</v>
       </c>
       <c r="B327" t="s">
@@ -20502,7 +20505,7 @@
       </c>
     </row>
     <row r="328" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A328" s="47">
+      <c r="A328" s="41">
         <v>12502</v>
       </c>
       <c r="B328" t="s">
@@ -20519,7 +20522,7 @@
       </c>
     </row>
     <row r="329" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A329" s="47">
+      <c r="A329" s="41">
         <v>12502</v>
       </c>
       <c r="B329" t="s">
@@ -20587,7 +20590,7 @@
       </c>
     </row>
     <row r="333" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A333" s="47">
+      <c r="A333" s="41">
         <v>13801</v>
       </c>
       <c r="B333" t="s">
@@ -20604,7 +20607,7 @@
       </c>
     </row>
     <row r="334" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A334" s="47">
+      <c r="A334" s="41">
         <v>13801</v>
       </c>
       <c r="B334" t="s">
@@ -20624,7 +20627,7 @@
       </c>
     </row>
     <row r="335" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A335" s="47">
+      <c r="A335" s="41">
         <v>13801</v>
       </c>
       <c r="B335" t="s">
@@ -20644,7 +20647,7 @@
       </c>
     </row>
     <row r="336" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A336" s="47">
+      <c r="A336" s="41">
         <v>13801</v>
       </c>
       <c r="B336" t="s">
@@ -20664,7 +20667,7 @@
       </c>
     </row>
     <row r="337" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A337" s="47">
+      <c r="A337" s="41">
         <v>13801</v>
       </c>
       <c r="B337" t="s">
@@ -20953,7 +20956,7 @@
       </c>
     </row>
     <row r="354" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A354" s="47">
+      <c r="A354" s="41">
         <v>14302</v>
       </c>
       <c r="B354" t="s">
@@ -20970,7 +20973,7 @@
       </c>
     </row>
     <row r="355" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A355" s="47">
+      <c r="A355" s="41">
         <v>14302</v>
       </c>
       <c r="B355" t="s">
@@ -20987,7 +20990,7 @@
       </c>
     </row>
     <row r="356" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A356" s="47">
+      <c r="A356" s="41">
         <v>14302</v>
       </c>
       <c r="B356" t="s">
@@ -21004,7 +21007,7 @@
       </c>
     </row>
     <row r="357" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A357" s="47">
+      <c r="A357" s="41">
         <v>14302</v>
       </c>
       <c r="B357" t="s">
@@ -21021,7 +21024,7 @@
       </c>
     </row>
     <row r="358" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A358" s="47">
+      <c r="A358" s="41">
         <v>14302</v>
       </c>
       <c r="B358" t="s">
@@ -21038,7 +21041,7 @@
       </c>
     </row>
     <row r="359" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A359" s="47">
+      <c r="A359" s="41">
         <v>14302</v>
       </c>
       <c r="B359" t="s">
@@ -21055,7 +21058,7 @@
       </c>
     </row>
     <row r="360" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A360" s="47">
+      <c r="A360" s="41">
         <v>14302</v>
       </c>
       <c r="B360" t="s">
@@ -21072,7 +21075,7 @@
       </c>
     </row>
     <row r="361" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A361" s="47">
+      <c r="A361" s="41">
         <v>14302</v>
       </c>
       <c r="B361" t="s">
@@ -21089,7 +21092,7 @@
       </c>
     </row>
     <row r="362" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A362" s="47">
+      <c r="A362" s="41">
         <v>14302</v>
       </c>
       <c r="B362" t="s">
@@ -21106,7 +21109,7 @@
       </c>
     </row>
     <row r="363" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A363" s="47">
+      <c r="A363" s="41">
         <v>14302</v>
       </c>
       <c r="B363" t="s">
@@ -21123,7 +21126,7 @@
       </c>
     </row>
     <row r="364" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A364" s="47">
+      <c r="A364" s="41">
         <v>14302</v>
       </c>
       <c r="B364" t="s">
@@ -21140,7 +21143,7 @@
       </c>
     </row>
     <row r="365" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A365" s="47">
+      <c r="A365" s="41">
         <v>14302</v>
       </c>
       <c r="B365" t="s">
@@ -21157,7 +21160,7 @@
       </c>
     </row>
     <row r="366" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A366" s="47">
+      <c r="A366" s="41">
         <v>14302</v>
       </c>
       <c r="B366" t="s">
@@ -21174,7 +21177,7 @@
       </c>
     </row>
     <row r="367" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A367" s="47">
+      <c r="A367" s="41">
         <v>14302</v>
       </c>
       <c r="B367" t="s">
@@ -21191,7 +21194,7 @@
       </c>
     </row>
     <row r="368" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A368" s="47" t="s">
+      <c r="A368" s="41" t="s">
         <v>2159</v>
       </c>
       <c r="B368" t="s">
@@ -21208,7 +21211,7 @@
       </c>
     </row>
     <row r="369" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A369" s="47" t="s">
+      <c r="A369" s="41" t="s">
         <v>2159</v>
       </c>
       <c r="B369" t="s">
@@ -21225,7 +21228,7 @@
       </c>
     </row>
     <row r="370" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A370" s="47" t="s">
+      <c r="A370" s="41" t="s">
         <v>2159</v>
       </c>
       <c r="B370" t="s">
@@ -21242,7 +21245,7 @@
       </c>
     </row>
     <row r="371" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A371" s="47" t="s">
+      <c r="A371" s="41" t="s">
         <v>2159</v>
       </c>
       <c r="B371" t="s">
@@ -21259,7 +21262,7 @@
       </c>
     </row>
     <row r="372" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A372" s="47" t="s">
+      <c r="A372" s="41" t="s">
         <v>2159</v>
       </c>
       <c r="B372" t="s">
@@ -21276,7 +21279,7 @@
       </c>
     </row>
     <row r="373" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A373" s="47" t="s">
+      <c r="A373" s="41" t="s">
         <v>2159</v>
       </c>
       <c r="B373" t="s">
@@ -21293,7 +21296,7 @@
       </c>
     </row>
     <row r="374" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A374" s="47" t="s">
+      <c r="A374" s="41" t="s">
         <v>2159</v>
       </c>
       <c r="B374" t="s">
@@ -21310,7 +21313,7 @@
       </c>
     </row>
     <row r="375" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A375" s="47" t="s">
+      <c r="A375" s="41" t="s">
         <v>2159</v>
       </c>
       <c r="B375" t="s">
@@ -21327,7 +21330,7 @@
       </c>
     </row>
     <row r="376" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A376" s="47" t="s">
+      <c r="A376" s="41" t="s">
         <v>2159</v>
       </c>
       <c r="B376" t="s">
@@ -21344,7 +21347,7 @@
       </c>
     </row>
     <row r="377" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A377" s="47" t="s">
+      <c r="A377" s="41" t="s">
         <v>2159</v>
       </c>
       <c r="B377" t="s">
@@ -21361,7 +21364,7 @@
       </c>
     </row>
     <row r="378" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A378" s="47" t="s">
+      <c r="A378" s="41" t="s">
         <v>2159</v>
       </c>
       <c r="B378" t="s">
@@ -21378,7 +21381,7 @@
       </c>
     </row>
     <row r="379" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A379" s="47" t="s">
+      <c r="A379" s="41" t="s">
         <v>2159</v>
       </c>
       <c r="B379" t="s">
@@ -21395,7 +21398,7 @@
       </c>
     </row>
     <row r="380" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A380" s="47">
+      <c r="A380" s="41">
         <v>12301</v>
       </c>
       <c r="B380" t="s">
@@ -21412,7 +21415,7 @@
       </c>
     </row>
     <row r="381" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A381" s="47">
+      <c r="A381" s="41">
         <v>12301</v>
       </c>
       <c r="B381" t="s">
@@ -21429,7 +21432,7 @@
       </c>
     </row>
     <row r="382" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A382" s="47">
+      <c r="A382" s="41">
         <v>12301</v>
       </c>
       <c r="B382" t="s">
@@ -21446,7 +21449,7 @@
       </c>
     </row>
     <row r="383" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A383" s="47">
+      <c r="A383" s="41">
         <v>12301</v>
       </c>
       <c r="B383" t="s">
@@ -21463,7 +21466,7 @@
       </c>
     </row>
     <row r="384" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A384" s="47">
+      <c r="A384" s="41">
         <v>11402</v>
       </c>
       <c r="B384" t="s">
@@ -21480,7 +21483,7 @@
       </c>
     </row>
     <row r="385" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A385" s="47">
+      <c r="A385" s="41">
         <v>11402</v>
       </c>
       <c r="B385" t="s">
@@ -21497,7 +21500,7 @@
       </c>
     </row>
     <row r="386" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A386" s="47">
+      <c r="A386" s="41">
         <v>11402</v>
       </c>
       <c r="B386" t="s">
@@ -21514,7 +21517,7 @@
       </c>
     </row>
     <row r="387" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A387" s="47">
+      <c r="A387" s="41">
         <v>11402</v>
       </c>
       <c r="B387" t="s">
@@ -21531,7 +21534,7 @@
       </c>
     </row>
     <row r="388" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A388" s="47">
+      <c r="A388" s="41">
         <v>11402</v>
       </c>
       <c r="B388" t="s">
@@ -21548,7 +21551,7 @@
       </c>
     </row>
     <row r="389" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A389" s="47">
+      <c r="A389" s="41">
         <v>11402</v>
       </c>
       <c r="B389" t="s">
@@ -21565,7 +21568,7 @@
       </c>
     </row>
     <row r="390" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A390" s="47">
+      <c r="A390" s="41">
         <v>11402</v>
       </c>
       <c r="B390" t="s">
@@ -21582,7 +21585,7 @@
       </c>
     </row>
     <row r="391" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A391" s="47">
+      <c r="A391" s="41">
         <v>11402</v>
       </c>
       <c r="B391" t="s">
@@ -21599,7 +21602,7 @@
       </c>
     </row>
     <row r="392" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A392" s="47">
+      <c r="A392" s="41">
         <v>11402</v>
       </c>
       <c r="B392" t="s">
@@ -21616,7 +21619,7 @@
       </c>
     </row>
     <row r="393" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A393" s="47">
+      <c r="A393" s="41">
         <v>11402</v>
       </c>
       <c r="B393" t="s">
@@ -21633,7 +21636,7 @@
       </c>
     </row>
     <row r="394" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A394" s="47">
+      <c r="A394" s="41">
         <v>11402</v>
       </c>
       <c r="B394" t="s">
@@ -21650,7 +21653,7 @@
       </c>
     </row>
     <row r="395" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A395" s="47" t="s">
+      <c r="A395" s="41" t="s">
         <v>2136</v>
       </c>
       <c r="B395" t="s">
@@ -21667,7 +21670,7 @@
       </c>
     </row>
     <row r="396" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A396" s="47" t="s">
+      <c r="A396" s="41" t="s">
         <v>2136</v>
       </c>
       <c r="B396" t="s">
@@ -21684,7 +21687,7 @@
       </c>
     </row>
     <row r="397" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A397" s="47" t="s">
+      <c r="A397" s="41" t="s">
         <v>2136</v>
       </c>
       <c r="B397" t="s">
@@ -21701,7 +21704,7 @@
       </c>
     </row>
     <row r="398" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A398" s="47" t="s">
+      <c r="A398" s="41" t="s">
         <v>2136</v>
       </c>
       <c r="B398" t="s">
@@ -21718,7 +21721,7 @@
       </c>
     </row>
     <row r="399" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A399" s="47" t="s">
+      <c r="A399" s="41" t="s">
         <v>2136</v>
       </c>
       <c r="B399" t="s">
@@ -21735,7 +21738,7 @@
       </c>
     </row>
     <row r="400" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A400" s="47" t="s">
+      <c r="A400" s="41" t="s">
         <v>2136</v>
       </c>
       <c r="B400" t="s">
@@ -21752,7 +21755,7 @@
       </c>
     </row>
     <row r="401" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A401" s="47" t="s">
+      <c r="A401" s="41" t="s">
         <v>2136</v>
       </c>
       <c r="B401" t="s">
@@ -21769,7 +21772,7 @@
       </c>
     </row>
     <row r="402" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A402" s="47" t="s">
+      <c r="A402" s="41" t="s">
         <v>2136</v>
       </c>
       <c r="B402" t="s">
@@ -21786,7 +21789,7 @@
       </c>
     </row>
     <row r="403" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A403" s="47" t="s">
+      <c r="A403" s="41" t="s">
         <v>2136</v>
       </c>
       <c r="B403" t="s">
@@ -21803,7 +21806,7 @@
       </c>
     </row>
     <row r="404" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A404" s="47" t="s">
+      <c r="A404" s="41" t="s">
         <v>2136</v>
       </c>
       <c r="B404" t="s">
@@ -21820,7 +21823,7 @@
       </c>
     </row>
     <row r="405" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A405" s="47">
+      <c r="A405" s="41">
         <v>12701</v>
       </c>
       <c r="B405" t="s">
@@ -21837,7 +21840,7 @@
       </c>
     </row>
     <row r="406" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A406" s="47">
+      <c r="A406" s="41">
         <v>12701</v>
       </c>
       <c r="B406" t="s">
@@ -21905,7 +21908,7 @@
       </c>
     </row>
     <row r="410" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A410" s="47">
+      <c r="A410" s="41">
         <v>11503</v>
       </c>
       <c r="B410" t="s">
@@ -21922,7 +21925,7 @@
       </c>
     </row>
     <row r="411" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A411" s="47">
+      <c r="A411" s="41">
         <v>11503</v>
       </c>
       <c r="B411" t="s">
@@ -21939,7 +21942,7 @@
       </c>
     </row>
     <row r="412" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A412" s="47">
+      <c r="A412" s="41">
         <v>11503</v>
       </c>
       <c r="B412" t="s">
@@ -21956,7 +21959,7 @@
       </c>
     </row>
     <row r="413" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A413" s="47">
+      <c r="A413" s="41">
         <v>11503</v>
       </c>
       <c r="B413" t="s">
@@ -21973,7 +21976,7 @@
       </c>
     </row>
     <row r="414" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A414" s="47">
+      <c r="A414" s="41">
         <v>11503</v>
       </c>
       <c r="B414" t="s">
@@ -21990,7 +21993,7 @@
       </c>
     </row>
     <row r="415" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A415" s="47">
+      <c r="A415" s="41">
         <v>11503</v>
       </c>
       <c r="B415" t="s">
@@ -22007,7 +22010,7 @@
       </c>
     </row>
     <row r="416" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A416" s="47">
+      <c r="A416" s="41">
         <v>11503</v>
       </c>
       <c r="B416" t="s">
@@ -22024,7 +22027,7 @@
       </c>
     </row>
     <row r="417" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A417" s="47">
+      <c r="A417" s="41">
         <v>11503</v>
       </c>
       <c r="B417" t="s">
@@ -22041,7 +22044,7 @@
       </c>
     </row>
     <row r="418" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A418" s="47">
+      <c r="A418" s="41">
         <v>12702</v>
       </c>
       <c r="B418" t="s">
@@ -22058,7 +22061,7 @@
       </c>
     </row>
     <row r="419" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A419" s="47">
+      <c r="A419" s="41">
         <v>12702</v>
       </c>
       <c r="B419" t="s">
@@ -22075,7 +22078,7 @@
       </c>
     </row>
     <row r="420" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A420" s="47">
+      <c r="A420" s="41">
         <v>12702</v>
       </c>
       <c r="B420" t="s">
@@ -22092,7 +22095,7 @@
       </c>
     </row>
     <row r="421" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A421" s="47">
+      <c r="A421" s="41">
         <v>12702</v>
       </c>
       <c r="B421" t="s">
@@ -22109,7 +22112,7 @@
       </c>
     </row>
     <row r="422" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A422" s="47">
+      <c r="A422" s="41">
         <v>12702</v>
       </c>
       <c r="B422" t="s">
@@ -22126,7 +22129,7 @@
       </c>
     </row>
     <row r="423" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A423" s="47">
+      <c r="A423" s="41">
         <v>12702</v>
       </c>
       <c r="B423" t="s">
@@ -22143,7 +22146,7 @@
       </c>
     </row>
     <row r="424" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A424" s="47">
+      <c r="A424" s="41">
         <v>11504</v>
       </c>
       <c r="B424" t="s">
@@ -22160,7 +22163,7 @@
       </c>
     </row>
     <row r="425" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A425" s="47">
+      <c r="A425" s="41">
         <v>11504</v>
       </c>
       <c r="B425" t="s">
@@ -22177,7 +22180,7 @@
       </c>
     </row>
     <row r="426" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A426" s="47">
+      <c r="A426" s="41">
         <v>11504</v>
       </c>
       <c r="B426" t="s">
@@ -22194,7 +22197,7 @@
       </c>
     </row>
     <row r="427" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A427" s="47">
+      <c r="A427" s="41">
         <v>11504</v>
       </c>
       <c r="B427" t="s">
@@ -22211,7 +22214,7 @@
       </c>
     </row>
     <row r="428" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A428" s="47">
+      <c r="A428" s="41">
         <v>11504</v>
       </c>
       <c r="B428" t="s">
@@ -22228,7 +22231,7 @@
       </c>
     </row>
     <row r="429" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A429" s="47">
+      <c r="A429" s="41">
         <v>11504</v>
       </c>
       <c r="B429" t="s">
@@ -22245,7 +22248,7 @@
       </c>
     </row>
     <row r="430" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A430" s="47">
+      <c r="A430" s="41">
         <v>11504</v>
       </c>
       <c r="B430" t="s">
@@ -22262,7 +22265,7 @@
       </c>
     </row>
     <row r="431" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A431" s="47">
+      <c r="A431" s="41">
         <v>12503</v>
       </c>
       <c r="B431" t="s">
@@ -22279,7 +22282,7 @@
       </c>
     </row>
     <row r="432" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A432" s="47">
+      <c r="A432" s="41">
         <v>12503</v>
       </c>
       <c r="B432" t="s">
@@ -22296,7 +22299,7 @@
       </c>
     </row>
     <row r="433" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A433" s="47">
+      <c r="A433" s="41">
         <v>12503</v>
       </c>
       <c r="B433" t="s">
@@ -22313,7 +22316,7 @@
       </c>
     </row>
     <row r="434" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A434" s="47">
+      <c r="A434" s="41">
         <v>12503</v>
       </c>
       <c r="B434" t="s">
@@ -22330,7 +22333,7 @@
       </c>
     </row>
     <row r="435" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A435" s="47">
+      <c r="A435" s="41">
         <v>11102</v>
       </c>
       <c r="B435" t="s">
@@ -22347,7 +22350,7 @@
       </c>
     </row>
     <row r="436" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A436" s="47">
+      <c r="A436" s="41">
         <v>11102</v>
       </c>
       <c r="B436" t="s">
@@ -22364,7 +22367,7 @@
       </c>
     </row>
     <row r="437" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A437" s="47">
+      <c r="A437" s="41">
         <v>11102</v>
       </c>
       <c r="B437" t="s">
@@ -22381,7 +22384,7 @@
       </c>
     </row>
     <row r="438" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A438" s="47">
+      <c r="A438" s="41">
         <v>11102</v>
       </c>
       <c r="B438" t="s">
@@ -22398,7 +22401,7 @@
       </c>
     </row>
     <row r="439" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A439" s="47">
+      <c r="A439" s="41">
         <v>11102</v>
       </c>
       <c r="B439" t="s">
@@ -22415,7 +22418,7 @@
       </c>
     </row>
     <row r="440" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A440" s="47">
+      <c r="A440" s="41">
         <v>11102</v>
       </c>
       <c r="B440" t="s">
@@ -22432,7 +22435,7 @@
       </c>
     </row>
     <row r="441" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A441" s="47">
+      <c r="A441" s="41">
         <v>11102</v>
       </c>
       <c r="B441" t="s">
@@ -22755,7 +22758,7 @@
       </c>
     </row>
     <row r="460" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A460" s="47">
+      <c r="A460" s="41">
         <v>10802</v>
       </c>
       <c r="B460" s="32" t="s">
@@ -22772,7 +22775,7 @@
       </c>
     </row>
     <row r="461" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A461" s="47">
+      <c r="A461" s="41">
         <v>10802</v>
       </c>
       <c r="B461" s="32" t="s">
@@ -22789,7 +22792,7 @@
       </c>
     </row>
     <row r="462" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A462" s="47">
+      <c r="A462" s="41">
         <v>10802</v>
       </c>
       <c r="B462" s="32" t="s">
@@ -22806,7 +22809,7 @@
       </c>
     </row>
     <row r="463" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A463" s="47">
+      <c r="A463" s="41">
         <v>10802</v>
       </c>
       <c r="B463" s="32" t="s">
@@ -22823,7 +22826,7 @@
       </c>
     </row>
     <row r="464" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A464" s="47">
+      <c r="A464" s="41">
         <v>10802</v>
       </c>
       <c r="B464" s="32" t="s">
@@ -22840,7 +22843,7 @@
       </c>
     </row>
     <row r="465" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A465" s="47">
+      <c r="A465" s="41">
         <v>10802</v>
       </c>
       <c r="B465" s="32" t="s">
@@ -22857,7 +22860,7 @@
       </c>
     </row>
     <row r="466" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A466" s="47">
+      <c r="A466" s="41">
         <v>10802</v>
       </c>
       <c r="B466" s="32" t="s">
@@ -22874,7 +22877,7 @@
       </c>
     </row>
     <row r="467" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A467" s="47">
+      <c r="A467" s="41">
         <v>10802</v>
       </c>
       <c r="B467" s="32" t="s">
@@ -22891,7 +22894,7 @@
       </c>
     </row>
     <row r="468" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A468" s="47">
+      <c r="A468" s="41">
         <v>10802</v>
       </c>
       <c r="B468" s="32" t="s">
@@ -22908,7 +22911,7 @@
       </c>
     </row>
     <row r="469" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A469" s="47">
+      <c r="A469" s="41">
         <v>10802</v>
       </c>
       <c r="B469" s="32" t="s">
@@ -22925,7 +22928,7 @@
       </c>
     </row>
     <row r="470" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A470" s="47">
+      <c r="A470" s="41">
         <v>12002</v>
       </c>
       <c r="B470" t="s">
@@ -22939,7 +22942,7 @@
       </c>
     </row>
     <row r="471" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A471" s="47">
+      <c r="A471" s="41">
         <v>12002</v>
       </c>
       <c r="B471" t="s">
@@ -22953,7 +22956,7 @@
       </c>
     </row>
     <row r="472" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A472" s="47">
+      <c r="A472" s="41">
         <v>12002</v>
       </c>
       <c r="B472" t="s">
@@ -22967,7 +22970,7 @@
       </c>
     </row>
     <row r="473" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A473" s="47">
+      <c r="A473" s="41">
         <v>12002</v>
       </c>
       <c r="B473" t="s">
@@ -22981,7 +22984,7 @@
       </c>
     </row>
     <row r="474" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A474" s="47">
+      <c r="A474" s="41">
         <v>12002</v>
       </c>
       <c r="B474" t="s">
@@ -22995,7 +22998,7 @@
       </c>
     </row>
     <row r="475" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A475" s="47">
+      <c r="A475" s="41">
         <v>12002</v>
       </c>
       <c r="B475" t="s">
@@ -23009,7 +23012,7 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="C30:C31">
+  <conditionalFormatting sqref="C11:C12">
     <cfRule type="duplicateValues" dxfId="7" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C47:C57">
@@ -23030,8 +23033,8 @@
   <conditionalFormatting sqref="C442:C459">
     <cfRule type="duplicateValues" dxfId="1" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C468:C1048576 D405:D406 C301:C353 C368:C441 C178:C297 C85:C167 C58:C70 C1:C29 C33:C46">
-    <cfRule type="duplicateValues" dxfId="0" priority="8"/>
+  <conditionalFormatting sqref="C468:C1048576 D405:D406 C301:C353 C368:C441 C178:C297 C85:C167 C58:C70 C1:C10 C14:C46">
+    <cfRule type="duplicateValues" dxfId="0" priority="185"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="1200" r:id="rId1"/>
@@ -23081,221 +23084,221 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B2" s="42" t="s">
+      <c r="B2" s="43" t="s">
         <v>1909</v>
       </c>
-      <c r="C2" s="43"/>
-      <c r="D2" s="43"/>
-      <c r="E2" s="44"/>
+      <c r="C2" s="44"/>
+      <c r="D2" s="44"/>
+      <c r="E2" s="45"/>
     </row>
     <row r="3" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B3" s="33" t="s">
         <v>1910</v>
       </c>
-      <c r="C3" s="41" t="s">
+      <c r="C3" s="42" t="s">
         <v>1911</v>
       </c>
-      <c r="D3" s="41"/>
-      <c r="E3" s="41"/>
-      <c r="F3" s="41"/>
-      <c r="G3" s="41"/>
-      <c r="H3" s="41"/>
-      <c r="I3" s="41"/>
-      <c r="J3" s="41"/>
-      <c r="K3" s="41"/>
-      <c r="L3" s="41"/>
-      <c r="M3" s="41"/>
-      <c r="N3" s="41"/>
+      <c r="D3" s="42"/>
+      <c r="E3" s="42"/>
+      <c r="F3" s="42"/>
+      <c r="G3" s="42"/>
+      <c r="H3" s="42"/>
+      <c r="I3" s="42"/>
+      <c r="J3" s="42"/>
+      <c r="K3" s="42"/>
+      <c r="L3" s="42"/>
+      <c r="M3" s="42"/>
+      <c r="N3" s="42"/>
     </row>
     <row r="4" spans="2:14" ht="62.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="33" t="s">
         <v>1912</v>
       </c>
-      <c r="C4" s="45" t="s">
+      <c r="C4" s="46" t="s">
         <v>1913</v>
       </c>
-      <c r="D4" s="45"/>
-      <c r="E4" s="45"/>
-      <c r="F4" s="45"/>
-      <c r="G4" s="45"/>
-      <c r="H4" s="45"/>
-      <c r="I4" s="45"/>
-      <c r="J4" s="45"/>
-      <c r="K4" s="45"/>
-      <c r="L4" s="45"/>
-      <c r="M4" s="45"/>
-      <c r="N4" s="45"/>
+      <c r="D4" s="46"/>
+      <c r="E4" s="46"/>
+      <c r="F4" s="46"/>
+      <c r="G4" s="46"/>
+      <c r="H4" s="46"/>
+      <c r="I4" s="46"/>
+      <c r="J4" s="46"/>
+      <c r="K4" s="46"/>
+      <c r="L4" s="46"/>
+      <c r="M4" s="46"/>
+      <c r="N4" s="46"/>
     </row>
     <row r="5" spans="2:14" ht="30" x14ac:dyDescent="0.25">
       <c r="B5" s="34" t="s">
         <v>1914</v>
       </c>
-      <c r="C5" s="41" t="s">
+      <c r="C5" s="42" t="s">
         <v>1915</v>
       </c>
-      <c r="D5" s="41"/>
-      <c r="E5" s="41"/>
-      <c r="F5" s="41"/>
-      <c r="G5" s="41"/>
-      <c r="H5" s="41"/>
-      <c r="I5" s="41"/>
-      <c r="J5" s="41"/>
-      <c r="K5" s="41"/>
-      <c r="L5" s="41"/>
-      <c r="M5" s="41"/>
-      <c r="N5" s="41"/>
+      <c r="D5" s="42"/>
+      <c r="E5" s="42"/>
+      <c r="F5" s="42"/>
+      <c r="G5" s="42"/>
+      <c r="H5" s="42"/>
+      <c r="I5" s="42"/>
+      <c r="J5" s="42"/>
+      <c r="K5" s="42"/>
+      <c r="L5" s="42"/>
+      <c r="M5" s="42"/>
+      <c r="N5" s="42"/>
     </row>
     <row r="6" spans="2:14" ht="30" x14ac:dyDescent="0.25">
       <c r="B6" s="35" t="s">
         <v>1916</v>
       </c>
-      <c r="C6" s="46" t="s">
+      <c r="C6" s="47" t="s">
         <v>1917</v>
       </c>
-      <c r="D6" s="46"/>
-      <c r="E6" s="46"/>
-      <c r="F6" s="46"/>
-      <c r="G6" s="46"/>
-      <c r="H6" s="46"/>
-      <c r="I6" s="46"/>
-      <c r="J6" s="46"/>
-      <c r="K6" s="46"/>
-      <c r="L6" s="46"/>
-      <c r="M6" s="46"/>
-      <c r="N6" s="46"/>
+      <c r="D6" s="47"/>
+      <c r="E6" s="47"/>
+      <c r="F6" s="47"/>
+      <c r="G6" s="47"/>
+      <c r="H6" s="47"/>
+      <c r="I6" s="47"/>
+      <c r="J6" s="47"/>
+      <c r="K6" s="47"/>
+      <c r="L6" s="47"/>
+      <c r="M6" s="47"/>
+      <c r="N6" s="47"/>
     </row>
     <row r="7" spans="2:14" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="36" t="s">
         <v>1918</v>
       </c>
-      <c r="C7" s="41" t="s">
+      <c r="C7" s="42" t="s">
         <v>1919</v>
       </c>
-      <c r="D7" s="41"/>
-      <c r="E7" s="41"/>
-      <c r="F7" s="41"/>
-      <c r="G7" s="41"/>
-      <c r="H7" s="41"/>
-      <c r="I7" s="41"/>
-      <c r="J7" s="41"/>
-      <c r="K7" s="41"/>
-      <c r="L7" s="41"/>
-      <c r="M7" s="41"/>
-      <c r="N7" s="41"/>
+      <c r="D7" s="42"/>
+      <c r="E7" s="42"/>
+      <c r="F7" s="42"/>
+      <c r="G7" s="42"/>
+      <c r="H7" s="42"/>
+      <c r="I7" s="42"/>
+      <c r="J7" s="42"/>
+      <c r="K7" s="42"/>
+      <c r="L7" s="42"/>
+      <c r="M7" s="42"/>
+      <c r="N7" s="42"/>
     </row>
     <row r="8" spans="2:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="36" t="s">
         <v>1918</v>
       </c>
-      <c r="C8" s="41" t="s">
+      <c r="C8" s="42" t="s">
         <v>1920</v>
       </c>
-      <c r="D8" s="41"/>
-      <c r="E8" s="41"/>
-      <c r="F8" s="41"/>
-      <c r="G8" s="41"/>
-      <c r="H8" s="41"/>
-      <c r="I8" s="41"/>
-      <c r="J8" s="41"/>
-      <c r="K8" s="41"/>
-      <c r="L8" s="41"/>
-      <c r="M8" s="41"/>
-      <c r="N8" s="41"/>
+      <c r="D8" s="42"/>
+      <c r="E8" s="42"/>
+      <c r="F8" s="42"/>
+      <c r="G8" s="42"/>
+      <c r="H8" s="42"/>
+      <c r="I8" s="42"/>
+      <c r="J8" s="42"/>
+      <c r="K8" s="42"/>
+      <c r="L8" s="42"/>
+      <c r="M8" s="42"/>
+      <c r="N8" s="42"/>
     </row>
     <row r="9" spans="2:14" ht="33.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="36" t="s">
         <v>1918</v>
       </c>
-      <c r="C9" s="41" t="s">
+      <c r="C9" s="42" t="s">
         <v>1921</v>
       </c>
-      <c r="D9" s="41"/>
-      <c r="E9" s="41"/>
-      <c r="F9" s="41"/>
-      <c r="G9" s="41"/>
-      <c r="H9" s="41"/>
-      <c r="I9" s="41"/>
-      <c r="J9" s="41"/>
-      <c r="K9" s="41"/>
-      <c r="L9" s="41"/>
-      <c r="M9" s="41"/>
-      <c r="N9" s="41"/>
+      <c r="D9" s="42"/>
+      <c r="E9" s="42"/>
+      <c r="F9" s="42"/>
+      <c r="G9" s="42"/>
+      <c r="H9" s="42"/>
+      <c r="I9" s="42"/>
+      <c r="J9" s="42"/>
+      <c r="K9" s="42"/>
+      <c r="L9" s="42"/>
+      <c r="M9" s="42"/>
+      <c r="N9" s="42"/>
     </row>
     <row r="10" spans="2:14" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="36" t="s">
         <v>1918</v>
       </c>
-      <c r="C10" s="41" t="s">
+      <c r="C10" s="42" t="s">
         <v>1922</v>
       </c>
-      <c r="D10" s="41"/>
-      <c r="E10" s="41"/>
-      <c r="F10" s="41"/>
-      <c r="G10" s="41"/>
-      <c r="H10" s="41"/>
-      <c r="I10" s="41"/>
-      <c r="J10" s="41"/>
-      <c r="K10" s="41"/>
-      <c r="L10" s="41"/>
-      <c r="M10" s="41"/>
-      <c r="N10" s="41"/>
+      <c r="D10" s="42"/>
+      <c r="E10" s="42"/>
+      <c r="F10" s="42"/>
+      <c r="G10" s="42"/>
+      <c r="H10" s="42"/>
+      <c r="I10" s="42"/>
+      <c r="J10" s="42"/>
+      <c r="K10" s="42"/>
+      <c r="L10" s="42"/>
+      <c r="M10" s="42"/>
+      <c r="N10" s="42"/>
     </row>
     <row r="11" spans="2:14" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="36" t="s">
         <v>1918</v>
       </c>
-      <c r="C11" s="41" t="s">
+      <c r="C11" s="42" t="s">
         <v>1923</v>
       </c>
-      <c r="D11" s="41"/>
-      <c r="E11" s="41"/>
-      <c r="F11" s="41"/>
-      <c r="G11" s="41"/>
-      <c r="H11" s="41"/>
-      <c r="I11" s="41"/>
-      <c r="J11" s="41"/>
-      <c r="K11" s="41"/>
-      <c r="L11" s="41"/>
-      <c r="M11" s="41"/>
-      <c r="N11" s="41"/>
+      <c r="D11" s="42"/>
+      <c r="E11" s="42"/>
+      <c r="F11" s="42"/>
+      <c r="G11" s="42"/>
+      <c r="H11" s="42"/>
+      <c r="I11" s="42"/>
+      <c r="J11" s="42"/>
+      <c r="K11" s="42"/>
+      <c r="L11" s="42"/>
+      <c r="M11" s="42"/>
+      <c r="N11" s="42"/>
     </row>
     <row r="12" spans="2:14" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="36" t="s">
         <v>1918</v>
       </c>
-      <c r="C12" s="41" t="s">
+      <c r="C12" s="42" t="s">
         <v>1924</v>
       </c>
-      <c r="D12" s="41"/>
-      <c r="E12" s="41"/>
-      <c r="F12" s="41"/>
-      <c r="G12" s="41"/>
-      <c r="H12" s="41"/>
-      <c r="I12" s="41"/>
-      <c r="J12" s="41"/>
-      <c r="K12" s="41"/>
-      <c r="L12" s="41"/>
-      <c r="M12" s="41"/>
-      <c r="N12" s="41"/>
+      <c r="D12" s="42"/>
+      <c r="E12" s="42"/>
+      <c r="F12" s="42"/>
+      <c r="G12" s="42"/>
+      <c r="H12" s="42"/>
+      <c r="I12" s="42"/>
+      <c r="J12" s="42"/>
+      <c r="K12" s="42"/>
+      <c r="L12" s="42"/>
+      <c r="M12" s="42"/>
+      <c r="N12" s="42"/>
     </row>
     <row r="13" spans="2:14" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="36" t="s">
         <v>1918</v>
       </c>
-      <c r="C13" s="41" t="s">
+      <c r="C13" s="42" t="s">
         <v>1925</v>
       </c>
-      <c r="D13" s="41"/>
-      <c r="E13" s="41"/>
-      <c r="F13" s="41"/>
-      <c r="G13" s="41"/>
-      <c r="H13" s="41"/>
-      <c r="I13" s="41"/>
-      <c r="J13" s="41"/>
-      <c r="K13" s="41"/>
-      <c r="L13" s="41"/>
-      <c r="M13" s="41"/>
-      <c r="N13" s="41"/>
+      <c r="D13" s="42"/>
+      <c r="E13" s="42"/>
+      <c r="F13" s="42"/>
+      <c r="G13" s="42"/>
+      <c r="H13" s="42"/>
+      <c r="I13" s="42"/>
+      <c r="J13" s="42"/>
+      <c r="K13" s="42"/>
+      <c r="L13" s="42"/>
+      <c r="M13" s="42"/>
+      <c r="N13" s="42"/>
     </row>
     <row r="14" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B14" s="37"/>
@@ -23306,224 +23309,236 @@
       <c r="G14" s="38"/>
     </row>
     <row r="15" spans="2:14" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="42" t="s">
+      <c r="B15" s="43" t="s">
         <v>1909</v>
       </c>
-      <c r="C15" s="43"/>
-      <c r="D15" s="43"/>
-      <c r="E15" s="44"/>
+      <c r="C15" s="44"/>
+      <c r="D15" s="44"/>
+      <c r="E15" s="45"/>
     </row>
     <row r="16" spans="2:14" ht="44.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="33" t="s">
         <v>1926</v>
       </c>
-      <c r="C16" s="41" t="s">
+      <c r="C16" s="42" t="s">
         <v>1927</v>
       </c>
-      <c r="D16" s="41"/>
-      <c r="E16" s="41"/>
-      <c r="F16" s="41"/>
-      <c r="G16" s="41"/>
-      <c r="H16" s="41"/>
-      <c r="I16" s="41"/>
-      <c r="J16" s="41"/>
-      <c r="K16" s="41"/>
-      <c r="L16" s="41"/>
-      <c r="M16" s="41"/>
-      <c r="N16" s="41"/>
+      <c r="D16" s="42"/>
+      <c r="E16" s="42"/>
+      <c r="F16" s="42"/>
+      <c r="G16" s="42"/>
+      <c r="H16" s="42"/>
+      <c r="I16" s="42"/>
+      <c r="J16" s="42"/>
+      <c r="K16" s="42"/>
+      <c r="L16" s="42"/>
+      <c r="M16" s="42"/>
+      <c r="N16" s="42"/>
     </row>
     <row r="17" spans="2:14" ht="71.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="33" t="s">
         <v>1912</v>
       </c>
-      <c r="C17" s="45" t="s">
+      <c r="C17" s="46" t="s">
         <v>1928</v>
       </c>
-      <c r="D17" s="45"/>
-      <c r="E17" s="45"/>
-      <c r="F17" s="45"/>
-      <c r="G17" s="45"/>
-      <c r="H17" s="45"/>
-      <c r="I17" s="45"/>
-      <c r="J17" s="45"/>
-      <c r="K17" s="45"/>
-      <c r="L17" s="45"/>
-      <c r="M17" s="45"/>
-      <c r="N17" s="45"/>
+      <c r="D17" s="46"/>
+      <c r="E17" s="46"/>
+      <c r="F17" s="46"/>
+      <c r="G17" s="46"/>
+      <c r="H17" s="46"/>
+      <c r="I17" s="46"/>
+      <c r="J17" s="46"/>
+      <c r="K17" s="46"/>
+      <c r="L17" s="46"/>
+      <c r="M17" s="46"/>
+      <c r="N17" s="46"/>
     </row>
     <row r="18" spans="2:14" ht="30" x14ac:dyDescent="0.25">
       <c r="B18" s="34" t="s">
         <v>1929</v>
       </c>
-      <c r="C18" s="41" t="s">
+      <c r="C18" s="42" t="s">
         <v>1930</v>
       </c>
-      <c r="D18" s="41"/>
-      <c r="E18" s="41"/>
-      <c r="F18" s="41"/>
-      <c r="G18" s="41"/>
-      <c r="H18" s="41"/>
-      <c r="I18" s="41"/>
-      <c r="J18" s="41"/>
-      <c r="K18" s="41"/>
-      <c r="L18" s="41"/>
-      <c r="M18" s="41"/>
-      <c r="N18" s="41"/>
+      <c r="D18" s="42"/>
+      <c r="E18" s="42"/>
+      <c r="F18" s="42"/>
+      <c r="G18" s="42"/>
+      <c r="H18" s="42"/>
+      <c r="I18" s="42"/>
+      <c r="J18" s="42"/>
+      <c r="K18" s="42"/>
+      <c r="L18" s="42"/>
+      <c r="M18" s="42"/>
+      <c r="N18" s="42"/>
     </row>
     <row r="19" spans="2:14" ht="45" x14ac:dyDescent="0.25">
       <c r="B19" s="35" t="s">
         <v>1931</v>
       </c>
-      <c r="C19" s="46" t="s">
+      <c r="C19" s="47" t="s">
         <v>1932</v>
       </c>
-      <c r="D19" s="46"/>
-      <c r="E19" s="46"/>
-      <c r="F19" s="46"/>
-      <c r="G19" s="46"/>
-      <c r="H19" s="46"/>
-      <c r="I19" s="46"/>
-      <c r="J19" s="46"/>
-      <c r="K19" s="46"/>
-      <c r="L19" s="46"/>
-      <c r="M19" s="46"/>
-      <c r="N19" s="46"/>
+      <c r="D19" s="47"/>
+      <c r="E19" s="47"/>
+      <c r="F19" s="47"/>
+      <c r="G19" s="47"/>
+      <c r="H19" s="47"/>
+      <c r="I19" s="47"/>
+      <c r="J19" s="47"/>
+      <c r="K19" s="47"/>
+      <c r="L19" s="47"/>
+      <c r="M19" s="47"/>
+      <c r="N19" s="47"/>
     </row>
     <row r="20" spans="2:14" ht="53.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="36" t="s">
         <v>1918</v>
       </c>
-      <c r="C20" s="41" t="s">
+      <c r="C20" s="42" t="s">
         <v>1933</v>
       </c>
-      <c r="D20" s="41"/>
-      <c r="E20" s="41"/>
-      <c r="F20" s="41"/>
-      <c r="G20" s="41"/>
-      <c r="H20" s="41"/>
-      <c r="I20" s="41"/>
-      <c r="J20" s="41"/>
-      <c r="K20" s="41"/>
-      <c r="L20" s="41"/>
-      <c r="M20" s="41"/>
-      <c r="N20" s="41"/>
+      <c r="D20" s="42"/>
+      <c r="E20" s="42"/>
+      <c r="F20" s="42"/>
+      <c r="G20" s="42"/>
+      <c r="H20" s="42"/>
+      <c r="I20" s="42"/>
+      <c r="J20" s="42"/>
+      <c r="K20" s="42"/>
+      <c r="L20" s="42"/>
+      <c r="M20" s="42"/>
+      <c r="N20" s="42"/>
     </row>
     <row r="21" spans="2:14" ht="26.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B21" s="36" t="s">
         <v>1918</v>
       </c>
-      <c r="C21" s="41" t="s">
+      <c r="C21" s="42" t="s">
         <v>1934</v>
       </c>
-      <c r="D21" s="41"/>
-      <c r="E21" s="41"/>
-      <c r="F21" s="41"/>
-      <c r="G21" s="41"/>
-      <c r="H21" s="41"/>
-      <c r="I21" s="41"/>
-      <c r="J21" s="41"/>
-      <c r="K21" s="41"/>
-      <c r="L21" s="41"/>
-      <c r="M21" s="41"/>
-      <c r="N21" s="41"/>
+      <c r="D21" s="42"/>
+      <c r="E21" s="42"/>
+      <c r="F21" s="42"/>
+      <c r="G21" s="42"/>
+      <c r="H21" s="42"/>
+      <c r="I21" s="42"/>
+      <c r="J21" s="42"/>
+      <c r="K21" s="42"/>
+      <c r="L21" s="42"/>
+      <c r="M21" s="42"/>
+      <c r="N21" s="42"/>
     </row>
     <row r="22" spans="2:14" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="36" t="s">
         <v>1918</v>
       </c>
-      <c r="C22" s="41" t="s">
+      <c r="C22" s="42" t="s">
         <v>1935</v>
       </c>
-      <c r="D22" s="41"/>
-      <c r="E22" s="41"/>
-      <c r="F22" s="41"/>
-      <c r="G22" s="41"/>
-      <c r="H22" s="41"/>
-      <c r="I22" s="41"/>
-      <c r="J22" s="41"/>
-      <c r="K22" s="41"/>
-      <c r="L22" s="41"/>
-      <c r="M22" s="41"/>
-      <c r="N22" s="41"/>
+      <c r="D22" s="42"/>
+      <c r="E22" s="42"/>
+      <c r="F22" s="42"/>
+      <c r="G22" s="42"/>
+      <c r="H22" s="42"/>
+      <c r="I22" s="42"/>
+      <c r="J22" s="42"/>
+      <c r="K22" s="42"/>
+      <c r="L22" s="42"/>
+      <c r="M22" s="42"/>
+      <c r="N22" s="42"/>
     </row>
     <row r="23" spans="2:14" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" s="36" t="s">
         <v>1918</v>
       </c>
-      <c r="C23" s="41" t="s">
+      <c r="C23" s="42" t="s">
         <v>1936</v>
       </c>
-      <c r="D23" s="41"/>
-      <c r="E23" s="41"/>
-      <c r="F23" s="41"/>
-      <c r="G23" s="41"/>
-      <c r="H23" s="41"/>
-      <c r="I23" s="41"/>
-      <c r="J23" s="41"/>
-      <c r="K23" s="41"/>
-      <c r="L23" s="41"/>
-      <c r="M23" s="41"/>
-      <c r="N23" s="41"/>
+      <c r="D23" s="42"/>
+      <c r="E23" s="42"/>
+      <c r="F23" s="42"/>
+      <c r="G23" s="42"/>
+      <c r="H23" s="42"/>
+      <c r="I23" s="42"/>
+      <c r="J23" s="42"/>
+      <c r="K23" s="42"/>
+      <c r="L23" s="42"/>
+      <c r="M23" s="42"/>
+      <c r="N23" s="42"/>
     </row>
     <row r="24" spans="2:14" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="36" t="s">
         <v>1918</v>
       </c>
-      <c r="C24" s="41" t="s">
+      <c r="C24" s="42" t="s">
         <v>1937</v>
       </c>
-      <c r="D24" s="41"/>
-      <c r="E24" s="41"/>
-      <c r="F24" s="41"/>
-      <c r="G24" s="41"/>
-      <c r="H24" s="41"/>
-      <c r="I24" s="41"/>
-      <c r="J24" s="41"/>
-      <c r="K24" s="41"/>
-      <c r="L24" s="41"/>
-      <c r="M24" s="41"/>
-      <c r="N24" s="41"/>
+      <c r="D24" s="42"/>
+      <c r="E24" s="42"/>
+      <c r="F24" s="42"/>
+      <c r="G24" s="42"/>
+      <c r="H24" s="42"/>
+      <c r="I24" s="42"/>
+      <c r="J24" s="42"/>
+      <c r="K24" s="42"/>
+      <c r="L24" s="42"/>
+      <c r="M24" s="42"/>
+      <c r="N24" s="42"/>
     </row>
     <row r="25" spans="2:14" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" s="36" t="s">
         <v>1918</v>
       </c>
-      <c r="C25" s="41" t="s">
+      <c r="C25" s="42" t="s">
         <v>1938</v>
       </c>
-      <c r="D25" s="41"/>
-      <c r="E25" s="41"/>
-      <c r="F25" s="41"/>
-      <c r="G25" s="41"/>
-      <c r="H25" s="41"/>
-      <c r="I25" s="41"/>
-      <c r="J25" s="41"/>
-      <c r="K25" s="41"/>
-      <c r="L25" s="41"/>
-      <c r="M25" s="41"/>
-      <c r="N25" s="41"/>
+      <c r="D25" s="42"/>
+      <c r="E25" s="42"/>
+      <c r="F25" s="42"/>
+      <c r="G25" s="42"/>
+      <c r="H25" s="42"/>
+      <c r="I25" s="42"/>
+      <c r="J25" s="42"/>
+      <c r="K25" s="42"/>
+      <c r="L25" s="42"/>
+      <c r="M25" s="42"/>
+      <c r="N25" s="42"/>
     </row>
     <row r="26" spans="2:14" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="36" t="s">
         <v>1918</v>
       </c>
-      <c r="C26" s="41" t="s">
+      <c r="C26" s="42" t="s">
         <v>1939</v>
       </c>
-      <c r="D26" s="41"/>
-      <c r="E26" s="41"/>
-      <c r="F26" s="41"/>
-      <c r="G26" s="41"/>
-      <c r="H26" s="41"/>
-      <c r="I26" s="41"/>
-      <c r="J26" s="41"/>
-      <c r="K26" s="41"/>
-      <c r="L26" s="41"/>
-      <c r="M26" s="41"/>
-      <c r="N26" s="41"/>
+      <c r="D26" s="42"/>
+      <c r="E26" s="42"/>
+      <c r="F26" s="42"/>
+      <c r="G26" s="42"/>
+      <c r="H26" s="42"/>
+      <c r="I26" s="42"/>
+      <c r="J26" s="42"/>
+      <c r="K26" s="42"/>
+      <c r="L26" s="42"/>
+      <c r="M26" s="42"/>
+      <c r="N26" s="42"/>
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="C26:N26"/>
+    <mergeCell ref="B15:E15"/>
+    <mergeCell ref="C16:N16"/>
+    <mergeCell ref="C17:N17"/>
+    <mergeCell ref="C18:N18"/>
+    <mergeCell ref="C19:N19"/>
+    <mergeCell ref="C20:N20"/>
+    <mergeCell ref="C21:N21"/>
+    <mergeCell ref="C22:N22"/>
+    <mergeCell ref="C23:N23"/>
+    <mergeCell ref="C24:N24"/>
+    <mergeCell ref="C25:N25"/>
     <mergeCell ref="C13:N13"/>
     <mergeCell ref="B2:E2"/>
     <mergeCell ref="C3:N3"/>
@@ -23536,30 +23551,20 @@
     <mergeCell ref="C10:N10"/>
     <mergeCell ref="C11:N11"/>
     <mergeCell ref="C12:N12"/>
-    <mergeCell ref="C26:N26"/>
-    <mergeCell ref="B15:E15"/>
-    <mergeCell ref="C16:N16"/>
-    <mergeCell ref="C17:N17"/>
-    <mergeCell ref="C18:N18"/>
-    <mergeCell ref="C19:N19"/>
-    <mergeCell ref="C20:N20"/>
-    <mergeCell ref="C21:N21"/>
-    <mergeCell ref="C22:N22"/>
-    <mergeCell ref="C23:N23"/>
-    <mergeCell ref="C24:N24"/>
-    <mergeCell ref="C25:N25"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="e7a156ab-dec1-49fa-a9cf-4ddad9eb4e7c" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7a5b9cf8-6f84-47d8-bb23-7f0863df71c6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -23792,20 +23797,27 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="e7a156ab-dec1-49fa-a9cf-4ddad9eb4e7c" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7a5b9cf8-6f84-47d8-bb23-7f0863df71c6">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7BB144D4-6990-4DC5-84D8-2F6804CA6F6C}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F620081A-8810-492F-90C1-DAC757933919}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="7a5b9cf8-6f84-47d8-bb23-7f0863df71c6"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="e7a156ab-dec1-49fa-a9cf-4ddad9eb4e7c"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -23830,18 +23842,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F620081A-8810-492F-90C1-DAC757933919}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7BB144D4-6990-4DC5-84D8-2F6804CA6F6C}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="7a5b9cf8-6f84-47d8-bb23-7f0863df71c6"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="e7a156ab-dec1-49fa-a9cf-4ddad9eb4e7c"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>